--- a/Endo_short_stature/Таблица источников.xlsx
+++ b/Endo_short_stature/Таблица источников.xlsx
@@ -15923,7 +15923,7 @@
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3">
@@ -15938,7 +15938,7 @@
       <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4">
@@ -15953,7 +15953,7 @@
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
@@ -15976,7 +15976,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6">
@@ -15999,7 +15999,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -16022,7 +16022,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8">
@@ -16045,7 +16045,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9">
@@ -16068,7 +16068,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -16091,7 +16091,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11">
@@ -16114,7 +16114,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -16137,7 +16137,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -16160,7 +16160,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14">
@@ -16183,7 +16183,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15">
@@ -16206,7 +16206,7 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16">
@@ -16229,7 +16229,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17">
@@ -16252,7 +16252,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18">
@@ -16275,7 +16275,7 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19">
@@ -16298,7 +16298,7 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20">
@@ -16321,7 +16321,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21">
@@ -16344,7 +16344,7 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22">
@@ -16367,7 +16367,7 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23">
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24">
@@ -16413,7 +16413,7 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25">
@@ -16436,7 +16436,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26">
@@ -16459,7 +16459,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27">
@@ -16482,7 +16482,7 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28">
@@ -16505,7 +16505,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>107</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29">
@@ -16528,7 +16528,7 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30">
@@ -16542,7 +16542,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>мнение экспертов Европейской референсной сети; текст её руководства без оценки качества</t>
+          <t>мнение экспертов Европейской референсной сети; текст её руководства без оценки качества; вторая причина: мнение докладчика</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31">
@@ -16574,7 +16574,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32">
@@ -16597,7 +16597,7 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33">
@@ -16620,7 +16620,7 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34">
@@ -16634,7 +16634,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Европейская референсная сеть: рекомендация и предложение; руководство по Тернеру: сильная рекомендация; опрос, n = 169</t>
+          <t>Европейская референсная сеть: рекомендация, предложение и текст обоснования; руководство по Тернеру: сильная рекомендация</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -16643,7 +16643,7 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>95</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35">
@@ -16666,7 +16666,7 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36">
@@ -16689,7 +16689,7 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37">
@@ -16712,7 +16712,7 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>84</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38">
@@ -16735,7 +16735,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39">
@@ -16758,7 +16758,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40">
@@ -16781,7 +16781,7 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41">
@@ -16827,7 +16827,7 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>113</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43">
@@ -16842,7 +16842,7 @@
       <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44">

--- a/Endo_short_stature/Таблица источников.xlsx
+++ b/Endo_short_stature/Таблица источников.xlsx
@@ -16045,7 +16045,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9">
@@ -16068,7 +16068,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
@@ -16183,7 +16183,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15">
@@ -16206,7 +16206,7 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16">
@@ -16321,7 +16321,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
@@ -16367,7 +16367,7 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23">
@@ -16459,7 +16459,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27">
@@ -16482,7 +16482,7 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28">
@@ -16505,7 +16505,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31">
@@ -16689,7 +16689,7 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37">
@@ -16735,7 +16735,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39">
@@ -16827,7 +16827,7 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43">

--- a/Endo_short_stature/Таблица источников.xlsx
+++ b/Endo_short_stature/Таблица источников.xlsx
@@ -431,11 +431,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:C110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="140" customWidth="1" min="2" max="2"/>
+    <col width="130" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -449,6 +450,11 @@
           <t>Источник</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Слайды</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -456,7 +462,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>van Trotsenburg P, et al. Thyroid 2021;31:387–419.</t>
+          <t>Adan L et al. J Clin Endocrinol Metab 1994;78:478–82</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -466,7 +477,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Persani L, et al. Eur Thyroid J 2018;7:225–237.</t>
+          <t>Akın Kağızmanlı G et al. J Clin Res Pediatr Endocrinol 2025;17:410–8</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -476,7 +492,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Fleseriu M, et al. Lancet Diabetes Endocrinol 2021;9:847–875.</t>
+          <t>Al-Ashwal AA et al. Horm Res Paediatr 2017;88:119–26</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -486,7 +507,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Tabarin A, et al. Ann Endocrinol (Paris) 2022;83:119–141.</t>
+          <t>Allen DB. Endocrinol Metab Clin North Am 1996;25:699–717</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -496,7 +522,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Martinerie L, et al. Ann Endocrinol (Paris) 2024;85:284–293.</t>
+          <t>Argente J et al. J Clin Endocrinol Metab 1997;82:2076–83</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -506,7 +537,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Korbonits M, et al. Nat Rev Endocrinol 2024;20:278–289 (часть 1).</t>
+          <t>Arlien-Søborg MC et al. Pituitary 2025;28:57 (GRS)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -516,7 +552,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Korbonits M, et al. Nat Rev Endocrinol 2024;20:290–309 (часть 2).</t>
+          <t>Ballerini MG et al. Horm Res Paediatr 2025;98:719–27</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>20, 21</t>
         </is>
       </c>
     </row>
@@ -526,7 +567,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Nordenström A, et al. Eur J Endocrinol 2022;186:G9–G49.</t>
+          <t>Baron J et al. Nat Rev Endocrinol 2015;11:735–46</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -536,7 +582,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Gravholt CH, et al. Eur J Endocrinol 2024;190:G53–G151.</t>
+          <t>Batista DL et al. Pediatrics 2007;120:e575–86</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -546,7 +597,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Boehm U, et al. Nat Rev Endocrinol 2015;11:547–564.</t>
+          <t>Bereket A et al. Horm Res 2006;65:96–105</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>36, 41</t>
         </is>
       </c>
     </row>
@@ -556,7 +612,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Grimberg A, et al. Horm Res Paediatr 2016;86:361–397.</t>
+          <t>Bidlingmaier M et al. J Clin Endocrinol Metab 2014;99:1712–21</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -566,7 +627,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Arlien-Søborg MC, et al. Pituitary 2025;28:57.</t>
+          <t>Binder G et al. Clin Endocrinol (Oxf) 2015;82:100–5</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -576,7 +642,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Mameli C, et al. Ital J Pediatr 2026;52(1). PMID 41723458. doi:10.1186/s13052-026-02215-8.</t>
+          <t>Blum WF et al. Pediatr Nephrol 1991;5:539–44</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>40, 42</t>
         </is>
       </c>
     </row>
@@ -586,7 +657,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Tanner JM, et al. Arch Dis Child 1970;45:755–762.</t>
+          <t>Boehm U et al. Nat Rev Endocrinol 2015;11:547–64</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>27, 34</t>
         </is>
       </c>
     </row>
@@ -596,7 +672,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Rivkees SA, et al. N Engl J Med 1988;318:599–602.</t>
+          <t>Boelen A et al. Handb Clin Neurol 2021;180:161–169</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -606,7 +687,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Persani L, et al. Endocrine 2021;71:681–688.</t>
+          <t>Boersma B et al. Eur J Pediatr 1996;155:362–7</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -616,7 +702,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Martin DD, et al. Horm Res Paediatr 2011;76:1–9.</t>
+          <t>Bucuvalas JC et al. Pediatr Transplant 1997;1:73–9</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -626,7 +717,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Salerno M, et al. Front Endocrinol (Lausanne) 2026;16:1744280.</t>
+          <t>Burns C et al. Growth Horm IGF Res 2009;19:457–62</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -636,7 +732,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Rohner F, et al. Thyroid 2020;30:898–907.</t>
+          <t>Cavallo F et al. Front Pediatr 2021;9:580314</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -646,7 +747,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Boersma B, et al. Eur J Pediatr 1996;155:362–367.</t>
+          <t>Cerbone M et al. Eur J Endocrinol 2011;164:591–7</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -656,7 +762,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Teng L, et al. J Pediatr Endocrinol Metab 2004;17:345–354.</t>
+          <t>Chanson P et al. J Clin Endocrinol Metab 2016;101:3450–8</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>37, 38</t>
         </is>
       </c>
     </row>
@@ -666,7 +777,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Minamitani K, et al. Arch Dis Child 1994;70:429–430.</t>
+          <t>Chernausek SD, Turner R. J Pediatr 1989;114:968–72</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>7, 40</t>
         </is>
       </c>
     </row>
@@ -676,7 +792,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Cerbone M, et al. Eur J Endocrinol 2011;164:591–597.</t>
+          <t>Cianfarani S et al. Horm Res Paediatr 2026, PMID 41553972</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -686,7 +807,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Wasniewska M, et al. Eur J Endocrinol 2009;160:417–421.</t>
+          <t>Cianfarani S et al. J Clin Endocrinol Metab 2005;90:6028–34</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -696,7 +822,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Zengin NŞ, et al. J Clin Res Pediatr Endocrinol 2026;18:498–507.</t>
+          <t>Clemmons DR. Clin Chem 2011;57:555–9</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -706,7 +837,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Persani L, et al. Endocr Connect 2019;8:R44–R54.</t>
+          <t>Coutant R et al. J Clin Endocrinol Metab 2010;95:5225–32</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -716,7 +852,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Boelen A, et al. Handb Clin Neurol 2021;180:161–169.</t>
+          <t>Covar RA et al. J Allergy Clin Immunol 2000;106:651–9</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -726,7 +867,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Wyatt DT, et al. J Clin Endocrinol Metab 1998;83:3493–3497.</t>
+          <t>Davies JH et al. Clin Endocrinol (Oxf) 2005;62:466–72</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>22, 23</t>
         </is>
       </c>
     </row>
@@ -736,7 +882,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Smyczyńska J, et al. Thyroid Res 2010;3:2.</t>
+          <t>De Benedetti F et al. Endocrinology 2001;142:4818–26</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -746,7 +897,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Niuro L, et al. Horm Res Paediatr 2023;96:376–384.</t>
+          <t>De Benedetti F et al. J Clin Invest 1997;99:643–50</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>40, 41</t>
         </is>
       </c>
     </row>
@@ -756,7 +912,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Greening JE, et al. J Endocrinol Invest 2006;29:885–887.</t>
+          <t>Eckert-Lind C et al. JAMA Pediatr 2020;174:e195881</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -766,7 +927,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Magiakou MA, et al. N Engl J Med 1994;331:629–636.</t>
+          <t>Emons J et al. Horm Res Paediatr 2011;75:383–91</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -776,7 +942,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Yamamoto M, et al. Endocr J 2026. PMID 42386546. doi:10.1507/endocrj.EJ26-0212.</t>
+          <t>Fazeli PK, Klibanski A. J Endocrinol 2014;220:R57–65</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -786,7 +957,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Stratakis CA. Endocrinol Metab Clin North Am 2012;41:793–803.</t>
+          <t>Federico G et al. Horm Res 1997;48:108–14</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -796,7 +972,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Allen DB. Endocrinol Metab Clin North Am 1996;25:699–717.</t>
+          <t>Fleseriu M et al. Lancet Diabetes Endocrinol 2021;9:847–75 (Pituitary Society)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>15, 19, 20, 21, 23</t>
         </is>
       </c>
     </row>
@@ -806,7 +987,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Hochberg Z. Horm Res 2002;58 Suppl 1:33–38.</t>
+          <t>Gadelha MR et al. J Clin Endocrinol Metab 1999;84:249–56</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -816,7 +1002,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Covar RA, et al. J Allergy Clin Immunol 2000;106:651–659.</t>
+          <t>Gafni RI et al. Pediatr Res 2001;50:618–23</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -826,7 +1017,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Simon D, et al. J Rheumatol 2002;29:1296–1300.</t>
+          <t>Gawlik-Starzyk A et al. Horm Res Paediatr 2025;98:327–35</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -836,7 +1032,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Zhang L, et al. Cochrane Database Syst Rev 2014;(7):CD009471.</t>
+          <t>Gravholt CH et al. Eur J Endocrinol 2024;190:G53–G151</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>30, 31, 32, 33, 34</t>
         </is>
       </c>
     </row>
@@ -846,7 +1047,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Kelly HW, et al. N Engl J Med 2012;367:904–912.</t>
+          <t>Gravholt CH et al. Lancet Diabetes Endocrinol 2026, PMID 42790437</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -856,7 +1062,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Skoner DP, et al. Pediatrics 2000;105:E23.</t>
+          <t>Greening JE et al. J Endocrinol Invest 2006;29:885–7</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -866,7 +1077,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Schenkel EJ, et al. Pediatrics 2000;105:E22.</t>
+          <t>Grumbach MM. J Pediatr Endocrinol Metab 2000;13 Suppl 6:1439–55</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -876,7 +1092,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Tempark T, et al. Endocrine 2010;38:328–334.</t>
+          <t>Guevara-Aguirre J et al. Rev Endocr Metab Disord 2021;22:59–70</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>40, 42</t>
         </is>
       </c>
     </row>
@@ -886,7 +1107,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Hassan M, et al. Horm Res Paediatr 2026;99:718–729.</t>
+          <t>Harrington J, Palmert MR. J Clin Endocrinol Metab 2012;97:3056–67</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -896,7 +1122,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Wasserman JD, et al. J Clin Oncol 2015;33:602–609.</t>
+          <t>Hassan M et al. Horm Res Paediatr 2026;99:718–29</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -906,7 +1137,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Batista DL, et al. Pediatrics 2007;120:e575–e586.</t>
+          <t>Hochberg Z. Horm Res 2002;58 Suppl 1:33–8</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>5, 16, 17</t>
         </is>
       </c>
     </row>
@@ -916,7 +1152,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Ballerini MG, et al. Horm Res Paediatr 2025;98:719–727.</t>
+          <t>Juul A et al. J Clin Endocrinol Metab 1994;78:744–52</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -926,7 +1167,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Magiakou MA, et al. J Clin Endocrinol Metab 1994;79:1082–1085.</t>
+          <t>Juul A. Hum Reprod Update 2001;7:303–13</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -936,7 +1182,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Lebrethon MC, et al. J Clin Endocrinol Metab 2000;85:3262–3265.</t>
+          <t>Kelly HW et al. N Engl J Med 2012;367:904–12</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -946,7 +1197,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Davies JH, et al. Clin Endocrinol (Oxf) 2005;62:466–472.</t>
+          <t>Kilic M et al. Clin Biochem 2004;37:382–7</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -956,7 +1212,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Wehkalampi K, et al. Horm Res 2007;68:99–104.</t>
+          <t>Korbonits M et al. Nat Rev Endocrinol 2024;20:290–309</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>19, 21</t>
         </is>
       </c>
     </row>
@@ -966,7 +1227,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Wehkalampi K, et al. J Clin Endocrinol Metab 2008;93:723–728.</t>
+          <t>Lebrethon MC et al. J Clin Endocrinol Metab 2000;85:3262–5</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -976,7 +1242,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Akın Kağızmanlı G, et al. J Clin Res Pediatr Endocrinol 2025;17:410–418.</t>
+          <t>Lui JC et al. Endocr Dev 2011;21:23–9</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -986,7 +1257,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Adan L, et al. J Clin Endocrinol Metab 1994;78:478–482.</t>
+          <t>Magiakou MA et al. J Clin Endocrinol Metab 1994;78:131–7</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -996,7 +1272,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Seppä S, et al. Eur J Endocrinol 2021;184:R225–R242.</t>
+          <t>Magiakou MA et al. J Clin Endocrinol Metab 1994;79:1082–5</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1287,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Eckert-Lind C, et al. JAMA Pediatr 2020;174:e195881.</t>
+          <t>Magiakou MA et al. N Engl J Med 1994;331:629–36</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>15, 19</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1302,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Sedlmeyer IL, Palmert MR. J Clin Endocrinol Metab 2002;87:1613–1620.</t>
+          <t>Mameli C et al. Ital J Pediatr 2026;52(1), PMID 41723458</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1317,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Varimo T, et al. Hum Reprod 2017;32:147–153.</t>
+          <t>Mameli C et al. Ital J Pediatr 2026;52(1), PMID 41723458 (описание метода Таннера: среднее роста родителей ±6,5 см)</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1332,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Binder G, et al. Clin Endocrinol (Oxf) 2015;82:100–105.</t>
+          <t>Marchini A et al. Endocr Rev 2016;37:417–48</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1347,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Coutant R, et al. J Clin Endocrinol Metab 2010;95:5225–5232.</t>
+          <t>Marino R et al. Endocrinology 2008;149:1820–8</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1362,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Harrington J, Palmert MR. J Clin Endocrinol Metab 2012;97:3056–3067.</t>
+          <t>Martin DD et al. Horm Res Paediatr 2011;76:1–9</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1377,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Gravholt CH, et al. Lancet Diabetes Endocrinol 2026. PMID 42790437. doi:10.1016/S2213-8587(26)00192-0.</t>
+          <t>Mazziotti G, Giustina A. Nat Rev Endocrinol 2013;9:265–76</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1392,12 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Wang L, et al. BMC Endocr Disord 2026;26(1). PMID 41933328. doi:10.1186/s12902-026-02253-7.</t>
+          <t>Minamitani K et al. Arch Dis Child 1994;70:429–30</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1407,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Gawlik-Starzyk A, et al. Horm Res Paediatr 2025;98:327–335.</t>
+          <t>Moia S et al. Ital J Pediatr 2017;43:94</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1422,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Ross JL, et al. N Engl J Med 2011;364:1230–1242.</t>
+          <t>Morishima A et al. J Clin Endocrinol Metab 1995;80:3689–98</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1437,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Shihadeh F, et al. Horm Res Paediatr 2026. PMID 42721063. doi:10.1159/hrp/adaag027.</t>
+          <t>Niuro L et al. Horm Res Paediatr 2023;96:376–84</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1452,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Cianfarani S, et al. Horm Res Paediatr 2026. PMID 41553972. doi:10.1159/000550518.</t>
+          <t>Nordenström A et al. Eur J Endocrinol 2022;186:G9–G49</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>25, 29, 33, 34</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1467,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Shen Y, et al. Eur J Pediatr 2015;174:419–427.</t>
+          <t>Persani L et al. Endocr Connect 2019;8:R44–R54</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1482,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Cianfarani S, et al. J Clin Endocrinol Metab 2005;90:6028–6034.</t>
+          <t>Persani L et al. Endocr Connect 2019;8:R44–R54; van Trotsenburg P et al. Thyroid 2021;31:387–419</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1497,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Wit JM, et al. J Clin Res Pediatr Endocrinol 2020;12:130–139.</t>
+          <t>Persani L et al. Endocrine 2021;71:681–8</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>4, 24, 25, 26, 27, 28, 29</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1512,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Bereket A, et al. Horm Res 2006;65:96–105.</t>
+          <t>Rinderknecht E, Humbel RE. J Biol Chem 1978;253:2769–76</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1527,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Juul A, et al. J Clin Endocrinol Metab 1994;78:744–752.</t>
+          <t>Rivkees SA et al. N Engl J Med 1988;318:599–602</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>4, 8, 10</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1542,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Clemmons DR. Clin Chem 2011;57:555–559.</t>
+          <t>Rohner F et al. Thyroid 2020;30:898–907</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1557,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Burns C, et al. Growth Horm IGF Res 2009;19:457–462.</t>
+          <t>Ross JL et al. N Engl J Med 2011;364:1230–42</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1572,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Chanson P, et al. J Clin Endocrinol Metab 2016;101:3450–3458.</t>
+          <t>Salerno M et al. Front Endocrinol (Lausanne) 2026;16:1744280</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>6, 9, 10</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1587,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Bidlingmaier M, et al. J Clin Endocrinol Metab 2014;99:1712–1721.</t>
+          <t>Schenkel EJ et al. Pediatrics 2000;105:E22</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1602,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Rinderknecht E, Humbel RE. J Biol Chem 1978;253:2769–2776.</t>
+          <t>Sedlmeyer IL, Palmert MR. J Clin Endocrinol Metab 2002;87:1613–20</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1617,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Zamboni G, et al. Acta Paediatr 2000;89:1050–1055.</t>
+          <t>Seppä S et al. Eur J Endocrinol 2021;184:R225–R242</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1632,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Zamboni G, et al. Pediatr Res 1996;39:410–414.</t>
+          <t>Shao YY et al. Rev Endocr Metab Disord 2006;7:265–71</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1647,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Kilic M, et al. Clin Biochem 2004;37:382–387.</t>
+          <t>Shen Y et al. Eur J Pediatr 2015;174:419–27</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1662,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Street ME, et al. Clin Endocrinol (Oxf) 2008;68:22–28.</t>
+          <t>Shihadeh F et al. Horm Res Paediatr 2026, PMID 42721063</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1677,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Federico G, et al. Horm Res 1997;48:108–114.</t>
+          <t>Simon D et al. J Rheumatol 2002;29:1296–300</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1692,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>De Benedetti F, et al. J Clin Invest 1997;99:643–650.</t>
+          <t>Skoner DP et al. Pediatrics 2000;105:E23</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1707,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>De Benedetti F, et al. Endocrinology 2001;142:4818–4826.</t>
+          <t>Smith EP et al. N Engl J Med 1994;331:1056–61</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1722,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Bucuvalas JC, et al. Pediatr Transplant 1997;1:73–79.</t>
+          <t>Smyczyńska J et al. Thyroid Res 2010;3:2</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1737,12 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Virmani A. Indian J Endocrinol Metab 2015;19 Suppl 1:S64–S67.</t>
+          <t>Stratakis CA. Endocrinol Metab Clin North Am 2012;41:793–803</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>16, 17, 19, 20, 21, 23</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1752,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Argente J, et al. J Clin Endocrinol Metab 1997;82:2076–2083.</t>
+          <t>Street ME et al. Clin Endocrinol (Oxf) 2008;68:22–8</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1767,12 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Magiakou MA, et al. J Clin Endocrinol Metab 1994;78:131–137.</t>
+          <t>Tanner JM et al. Arch Dis Child 1970;45:755–62 (центильные таблицы с поправкой на рост родителей)</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1782,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Blum WF, et al. Pediatr Nephrol 1991;5:539–544.</t>
+          <t>Tempark T et al. Endocrine 2010;38:328–34</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1797,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Tönshoff B, Fine RN. Adv Ren Replace Ther 1996;3:37–47.</t>
+          <t>Teng L et al. J Pediatr Endocrinol Metab 2004;17:345–54</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1812,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Guevara-Aguirre J, et al. Rev Endocr Metab Disord 2021;22:59–70.</t>
+          <t>Tönshoff B, Fine RN. Adv Ren Replace Ther 1996;3:37–47</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1827,12 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Al-Ashwal AA, et al. Horm Res Paediatr 2017;88:119–126.</t>
+          <t>Varimo T et al. Hum Reprod 2017;32:147–53</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>26, 27</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1842,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Moia S, et al. Ital J Pediatr 2017;43:94.</t>
+          <t>Virmani A. Indian J Endocrinol Metab 2015;19 Suppl 1:S64–7</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1857,12 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Gadelha MR, et al. J Clin Endocrinol Metab 1999;84:249–256.</t>
+          <t>Wang L et al. BMC Endocr Disord 2026;26(1), PMID 41933328</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1396,15 +1872,222 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Husby S, et al. J Pediatr Gastroenterol Nutr 2020;70:141–156.</t>
+          <t>Wasniewska M et al. Eur J Endocrinol 2009;160:417–21</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n"/>
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Изображения: все схемы кривых роста нарисованы автором как схемы, не данные пациентов; сторонних изображений нет.</t>
+          <t>Wasserman JD et al. J Clin Oncol 2015;33:602–9</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Wehkalampi K et al. Horm Res 2007;68:99–104</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Wehkalampi K et al. J Clin Endocrinol Metab 2008;93:723–8</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Weise M et al. Proc Natl Acad Sci USA 2001;98:6871–6</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>5, 29</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Williams GR, Bassett JHD. J Endocrinol Invest 2018;41:99–109</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12:130–9</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>35, 36, 39, 40, 41, 42</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Wong SC et al. Endocr Rev 2016;37:62–110</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Wyatt DT et al. J Clin Endocrinol Metab 1998;83:3493–7</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Yamamoto M et al. Endocr J 2026, PMID 42386546</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Zamboni G et al. Acta Paediatr 2000;89:1050–5</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Zamboni G et al. Pediatr Res 1996;39:410–4</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Zengin NŞ et al. J Clin Res Pediatr Endocrinol 2026;18:498–507</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Zhang L et al. Cochrane Database Syst Rev 2014;(7):CD009471</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>van Trotsenburg P et al. Thyroid 2021;31:387–419 (Endo-ERN, одобрено ESPE и ESE)</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -1419,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I300"/>
+  <dimension ref="A1:I328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12246,1823 +12929,1823 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>доп_S1</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>S1.01</t>
+          <t>M1.1</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Британский консенсус по аденомам гипофиза у детей (части 1 и 2) разработала многопрофильная группа экспертов в 2014–2022 годах с международной Дельфи-панелью; 74 рекомендации для детей и молодых людей до 19 лет, в части 1 их 17. Общества-издатели в аннотации не названы. Слайд 4, заметки.</t>
+          <t>Кость растёт в длину в зоне роста (эпифизарной пластинке): хондроциты (клетки хряща) делятся, затем увеличиваются в размерах (гипертрофия) и вырабатывают хрящевой матрикс; образовавшийся хрящ затем замещается костной тканью.</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Korbonits M, Blair JC, Boguslawska A et al. Nat Rev Endocrinol 2024;20(5):278–289 (часть 1)</t>
+          <t>Baron J, Sävendahl L, De Luca F, Dauber A, Phillip M, Wit JM, Nilsson O. Nat Rev Endocrinol 2015;11:735-46</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>38336897</t>
+          <t>26437621</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
         <is>
-          <t>10.1038/s41574-023-00948-8</t>
+          <t>10.1038/nrendo.2015.165</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Консенсус-руководство (поиск литературы и Дельфи)</t>
+          <t>обзор (полный текст)</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация</t>
+          <t>подтверждено</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>"a multidisciplinary expert group systematically developed the first comprehensive clinical practice consensus guideline for children and young people under the age 19 years … international Delphi consensus panel of experts … consolidated into 74 recommendations"</t>
+          <t>In the growth plate, chondrocytes proliferate, hypertrophy, and secrete cartilage extracellular matrix. These processes generate new cartilage tissue, which is subsequently remodeled into bone tissue.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>доп_S1</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>S1.02</t>
+          <t>M1.2</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>В систематическом обзоре 28 работ определяли низкорослость как рост ниже −2 СО, 19 работ брали процентильный порог (в основном 3-й центиль); 8 работ использовали оба определения, 3 работы определения не давали. Слайд 6, тело (строка 4) и заметки.</t>
+          <t>С возрастом зона роста «стареет»: деление хондроцитов замедляется, зона истончается, а в конце пубертата её хрящ полностью замещается костью (закрытие зоны роста), и рост в длину прекращается.</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Mameli C et al. Ital J Pediatr 2026;52(1)</t>
+          <t>Nilsson O, Baron J. Trends Endocrinol Metab 2004;15:370-4; Emons J, Chagin AS, Sävendahl L, Karperien M, Wit JM. Horm Res Paediatr 2011;75:383-91</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>41723458</t>
+          <t>15380808; 21540578</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>10.1186/s13052-026-02215-8</t>
+          <t>10.1016/j.tem.2004.08.004; 10.1159/000327788</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>Систематический обзор (PRISMA 2020; 35 клинических и 7 биохимических работ)</t>
+          <t>два обзора (по аннотациям)</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация</t>
+          <t>подтверждено</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>"28 studies used a threshold of &lt; 2 standard deviation score, while 19 applied percentile-based cut-offs (mostly the 3rd percentile); 8 studies considered both definitions, 3 studies do not report any definition."</t>
+          <t>During childhood, the growth plate matures, its total width decreases and eventually it disappears at the end of puberty with complete replacement by bone along with cessation of longitudinal growth.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>доп_S1</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>S1.03</t>
+          <t>M1.3</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>В работах обзора скорость роста и целевой рост использовали редко, хотя у них есть диагностическая ценность. Слайд 6, заметки.</t>
+          <t>В опытах на животных (глюкокортикоиды у кроликов, гипотиреоз у крыс) торможение роста замедляло и старение зоны роста. Поэтому считают, что старение определяется скорее самим ростом (по-видимому, накопленным числом делений клеток-предшественников хряща), чем возрастом как таковым; вклад возраста полностью не исключён. Прямых данных у человека нет.</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Mameli C et al. Ital J Pediatr 2026;52(1)</t>
+          <t>Lui JC, Nilsson O, Baron J. Endocr Dev 2011;21:23-9</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>41723458</t>
+          <t>21865751</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>10.1186/s13052-026-02215-8</t>
+          <t>10.1159/000328117</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>Систематический обзор</t>
+          <t>обзор; первичные данные получены в опытах на кроликах (глюкокортикоиды) и крысах (гипотиреоз)</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация</t>
+          <t>исправлено</t>
         </is>
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>"Growth velocity and target height were rarely used, despite their diagnostic value."</t>
+          <t>Conditions that slow growth in the growth plate also slow the entire development program of growth plate senescence, suggesting that the process of growth, rather than age per se, is the underlying driver of senescence.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>доп_S1</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>S1.04</t>
+          <t>M1.4</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>В работах обзора пользовались местными нормами роста, где они были; иначе чаще всего нормами ВОЗ и CDC. Какие нормы выбрать в Узбекистане и СНГ, обзор не говорит. Слайд 6, заметки.</t>
+          <t>После устранения причины, тормозившей рост (гипотиреоз, избыток глюкокортикоидов), возможен догоняющий рост: он идёт быстрее, чем положено по возрасту. В опытах на животных это объясняют тем, что при торможении зона роста стареет медленнее и ко времени выздоровления оказывается менее «старой», чем у сверстника. У людей подтверждение косвенное (дети с целиакией).</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Mameli C et al. Ital J Pediatr 2026;52(1)</t>
+          <t>Lui JC, Nilsson O, Baron J. Endocr Dev 2011;21:23-9</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>41723458</t>
+          <t>21865751</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>10.1186/s13052-026-02215-8</t>
+          <t>10.1159/000328117</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>Систематический обзор; описание практики, не рекомендация</t>
+          <t>обзор; механизм показан в опытах на кроликах и крысах, у людей данные косвенные</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация</t>
+          <t>исправлено</t>
         </is>
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>"Local growth charts were employed when available; otherwise, WHO and CDC references were most used."</t>
+          <t>Growth-inhibiting conditions such as glucocorticoid excess and hypothyroidism delay the program of growth plate senescence. Consequently, growth plates are less senescent after these conditions resolve and therefore grow more rapidly than is normal for age, resulting in catch-up growth.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>доп_S1</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>S1.05</t>
+          <t>M1.5</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Уточнение к 07.1a. Аннотация Martin 2011 прямо говорит об отставании костного возраста только у здоровых низкорослых детей. О дефиците СТГ сказано лишь, что на лечении СТГ костный возраст догоняет; «отстаёт при дефиците СТГ» — вывод, а не цитата. На слайде 7 оставлены только здоровые низкорослые дети.</t>
+          <t>При тяжёлом гипотиреозе костный возраст отстаёт, а слияние эпифизов задерживается. После лечения у детей с целиакией рост идёт быстрее, чем положено по паспортному возрасту, но соответствует более младшему возрасту (по росту или костному возрасту); это согласуется с гипотезой о задержке старения зоны роста. Прямого утверждения «отставание костного возраста равно задержке старения зоны роста» в источниках нет.</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Martin DD, Wit JM, Hochberg Z et al. Horm Res Paediatr 2011;76(1):1–9 (часть 1)</t>
+          <t>Lui JC, Nilsson O, Baron J. Endocr Dev 2011;21:23-9; Cavallo F, Mohn A, Chiarelli F, Giannini C. Front Pediatr 2021;9:580314</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>21691054</t>
+          <t>21865751; 33777857</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>10.1159/000329372</t>
+          <t>10.1159/000328117; 10.3389/fped.2021.580314</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>Нарративный обзор</t>
+          <t>два обзора; косвенные клинические данные (целиакия)</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>исправлено (часть о дефиците СТГ со слайда снята)</t>
+          <t>частично</t>
         </is>
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>"Healthy tall children tend to have advanced BA and healthy short children tend to have delayed BA in comparison to chronological age. Growth hormone (GH) treatment of children with GH deficiency leads to a catch-up in BA"</t>
+          <t>greater than expected for age (indicating catch-up growth) but normal for a younger child, based on their height age or bone age at the time of treatment initiation</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>доп_S1</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>S1.06</t>
+          <t>M2.1</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Arlien-Søborg 2025 — Дельфи-опрос по диагностике дефицита СТГ у детей и взрослых, начатый членами Общества по изучению гормона роста (GRS). Атрибуция ячейки таблицы слайда 4; содержание опроса — 38.2.</t>
+          <t>Гормон щитовидной железы (трийодтиронин) действует на хондроциты зоны роста и регулирует окостенение хряща; при гипотиреозе в детстве задерживается развитие скелета и нарушается созревание кости из-за дефекта окостенения хряща.</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Arlien-Søborg MC, Radovick S, Boguszewski MCS et al. Pituitary 2025;28(3):57</t>
+          <t>Williams GR, Bassett JHD. J Endocrinol Invest, 2018;41:99–109</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>40335774</t>
+          <t>28853052</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>10.1007/s11102-025-01526-z</t>
+          <t>10.1007/s40618-017-0753-4</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>Дельфи-опрос (педиатры n = 18, эндокринологи взрослых n = 25, 14 стран)</t>
+          <t>обзор (данные у людей и в опытах на мышах)</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация</t>
+          <t>исправлено</t>
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>"The Growth Hormone Research Society members initiated a Delphi survey of the diagnosis of GHD in children and adults."</t>
+          <t>T3 acts via TRα in chondrocytes and osteoblasts to regulate intramembranous and endochondral ossification … Hypothyroidism in childhood is relatively common and causes delayed skeletal development, growth retardation and short stature with impaired bone maturation due to defective endochondral ossification.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>доп_S2</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>S2.1a</t>
+          <t>M2.1b</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Ретроспективная когорта 111 детей с лёгким субклиническим гипотиреозом (ТТГ 5–10 мЕд/л минимум дважды, наблюдение ≥ 6 мес; идиопатические и с сопутствующими причинами): рост оставался в норме и у нелеченых не ухудшился; при идиопатической форме левотироксин понадобился 8,6 %. Всего: эутиреоз у 45 (40,5 %), стойкий субклинический у 49 (44,2 %), лечение у 17 (15,3 %). Слайд 12.</t>
+          <t>Гормон щитовидной железы регулирует переход клеток зоны роста от деления к созреванию (превращению в гипертрофированные хондроциты).</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Zengin NŞ, Sağsak E, Geylani Güleç S. J Clin Res Pediatr Endocrinol 2026;18(3):498–507</t>
+          <t>Shao YY, Wang L, Ballock RT. Rev Endocr Metab Disord 2006;7:265–71</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>41914440</t>
+          <t>17200892</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>10.4274/jcrpe.galenos.2026.2025-9-27</t>
+          <t>10.1007/s11154-006-9012-2</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Ретроспективная когорта, n = 111</t>
+          <t>обзор (по аннотации)</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация</t>
+          <t>подтверждено</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>"Idiopathic cases showed the most favorable course, with only 8.6% requiring therapy." … "Growth parameters remained within normal limits, with no deterioration in untreated children."</t>
+          <t>thyroid hormone regulates the critical transition between cell proliferation and terminal differentiation in the growth plate, specifically the maturation of growth plate chondrocytes into hypertrophic cells</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>доп_S2</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>S2.1b</t>
+          <t>M2.2</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>В той же когорте тиреоидит Хашимото — сильнейший предиктор прогрессии: левотироксин понадобился 42,1 % против 9,8 % без тиреоидита; ТТГ исходно &gt; 7,5 мЕд/л повышал вероятность лечения примерно в 3,5 раза. Слайд 12, заметки.</t>
+          <t>У детей с гипотиреозом задерживается развитие скелета и замедляется рост; при тяжёлом нелеченом гипотиреозе на рентгенограмме видны «крапчатые» эпифизы — признак эпифизарной дисгенезии (нарушенного формирования концов костей).</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Zengin NŞ et al. J Clin Res Pediatr Endocrinol 2026;18(3):498–507</t>
+          <t>Williams GR, Bassett JHD. J Endocrinol Invest, 2018;41:99–109</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>41914440</t>
+          <t>28853052</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>10.4274/jcrpe.galenos.2026.2025-9-27</t>
+          <t>10.1007/s40618-017-0753-4</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Ретроспективная когорта, n = 111</t>
+          <t>обзор</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация</t>
+          <t>частично</t>
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>"Hashimoto's thyroiditis (HT) was the strongest predictor of progression (42.1% vs. 9.8% in non-HT). A baseline TSH&gt;7.5 mIU/L increased treatment likelihood by ~3.5-fold."</t>
+          <t>Childhood hypothyroidism causes delayed skeletal development, retarded linear growth and impaired bone mineral accrual. Epiphyseal dysgenesis is evidenced by classic features of stippled epiphyses on X-ray.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>доп_S2</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>S2.2</t>
+          <t>M2.3</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Среди семи авторов обзора Salerno 2026 (источник доз левотироксина на слайде 10) есть сотрудник отдела медицинских вопросов фармацевтической компании (Centonze C). У двух других авторов та же строка приклеена к университетской аффилиации, вероятно, артефакт разбора. Что компания выпускает левотироксин, PubMed не сообщает, на слайд и в заметки не ставится. Слайд 10, заметки.</t>
+          <t>У детей с первичным гипотиреозом спонтанная ночная секреция СТГ снижена, и ИФР-1 в крови ниже, чем на фоне лечения левотироксином; после лечения оба показателя такие же, как у здоровых детей (небольшое исследование, 7 детей).</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Salerno M et al. Front Endocrinol (Lausanne) 2026;16:1744280</t>
+          <t>Chernausek SD, Turner R. J Pediatr, 1989;114:968–72</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>41585793</t>
+          <t>2723911</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
-          <t>10.3389/fendo.2025.1744280</t>
+          <t>10.1016/s0022-3476(89)80439-1</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>Аффилиация автора в записи PubMed</t>
+          <t>клиническое исследование (7 детей, сравнение до и во время лечения)</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: запись PubMed</t>
+          <t>исправлено</t>
         </is>
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>Centonze C: "Medical Affairs, Merck Serono SpA, Rome, Italy."</t>
+          <t>spontaneous GH secretion was consistently attenuated in the hypothyroid state … Coincident with the reduced levels of GH, plasma IGF-I concentrations were lower in patients before therapy</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>доп_S2</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>S2.3</t>
+          <t>M2.4</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Приобретённый центральный гипотиреоз связан в основном с объёмными образованиями гипоталамо-гипофизарной области; у детей самое частое такое образование — краниофарингиома. Слайд 13.</t>
+          <t>У крыс с гипотиреозом, вызванным пропилтиоурацилом, зона роста стареет медленнее; после отмены препарата это объясняет догоняющий рост.</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Persani L, Cangiano B, Bonomi M. Endocr Connect 2019;8(2):R44–R54</t>
+          <t>Marino R, Hegde A, Barnes KM, Schrier L, Emons JA, Nilsson O, Baron J. Endocrinology, 2008;149:1820–8</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>30645189</t>
+          <t>18174286</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>10.1530/EC-18-0515</t>
+          <t>10.1210/en.2007-0993</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>Экспертный обзор</t>
+          <t>опыты на новорождённых крысах</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст (PMC6373625)</t>
+          <t>подтверждено</t>
         </is>
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>"the acquired forms of CeH are mainly related to expansive lesions of the hypothalamic/pituitary region … Craniopharyngiomas represent the most prevalent expansive lesion associated with CeH in pediatric patients."</t>
+          <t>The findings demonstrate that growth inhibition due to hypothyroidism slows the developmental program of growth plate senescence, including the normal decline in the rate of longitudinal bone growth, thus accounting for catch-up growth.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>доп_S2</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>S2.4</t>
+          <t>M3.1</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Такие образования обычно нарушают функцию и гипофиза, и гипоталамуса, давая картину дефицита нескольких гормонов гипофиза. Слайд 13 (строка о причинах), слайд 14 (строка-ссылка).</t>
+          <t>Длительный избыток глюкокортикоидов, по традиционным представлениям, подавляет секрецию СТГ; влияние идёт на уровне гипоталамуса и гипофиза, а итог зависит от дозы и длительности воздействия.</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Persani L et al. Endocr Connect 2019;8(2):R44–R54</t>
+          <t>Mazziotti G, Giustina A. Nat Rev Endocrinol 2013;9:265–76</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>30645189</t>
+          <t>23381030</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>10.1530/EC-18-0515</t>
+          <t>10.1038/nrendo.2013.5</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>Экспертный обзор</t>
+          <t>обзор (описательный)</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст</t>
+          <t>частично</t>
         </is>
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>"these lesions usually affect both pituitary and hypothalamus function with a resulting MPHDs clinical picture"</t>
+          <t>The final effects of this modulation depend on hormone concentrations and the duration of exposure. The traditional hypothesis is that chronically raised levels of glucocorticoids suppress the secretion of GH.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>доп_S2</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>S2.5</t>
+          <t>M3.2</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>МРТ гипоталамо-гипофизарной области при впервые найденном центральном гипотиреозе.</t>
+          <t>Глюкокортикоиды нарушают работу оси СТГ — ИФР-1 не только в гипоталамусе и гипофизе, но и на уровне тканей-мишеней: меняют число рецепторов и передачу сигнала в клетке.</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Persani 2019 (полный текст); Persani 2018 ETA (аннотация); van Trotsenburg 2021 (полный текст)</t>
+          <t>Hochberg Z. Horm Res 2002;58 Suppl 1:33–8</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>30645189; 30374425; 33272083</t>
+          <t>12373012</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>10.1530/EC-18-0515; 10.1159/000491388; 10.1089/thy.2020.0333</t>
+          <t>10.1159/000064764</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>обзор (описательный)</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>не подтверждено (в доступных текстах МРТ не названа; полный текст ETA 2018 недоступен)</t>
+          <t>частично</t>
         </is>
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>Нет цитаты: поиск "MRI", "magnetic", "imaging" в полных текстах; в van Trotsenburg "imaging" только о щитовидной железе.</t>
+          <t>The GC interfere with the GH-IGF-1 axis at the hypothalamic, pituitary and target organ levels, affecting hormone release, receptor abundance, signal transduction, gene transcription, pre-mRNA splicing and mRNA translation.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>доп_S2</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>S2.6</t>
+          <t>M3.3</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Св. Т4 на лечении оценивают по крови, взятой до утренней дозы левотироксина или не раньше чем через 4 ч после неё, и в той же лаборатории. Слайд 13 (тело: «кровь до утренней таблетки»; заметки: 4 ч, та же лаборатория).</t>
+          <t>В зоне роста глюкокортикоиды прямо подавляют деление хондроцитов и синтез протеогликанов хрящевого матрикса, а в гипертрофированных (увеличенных) хондроцитах усиливают запрограммированную гибель клеток.</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Persani L et al. Endocr Connect 2019;8(2):R44–R54</t>
+          <t>Hochberg Z. Horm Res 2002;58 Suppl 1:33–8</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>30645189</t>
+          <t>12373012</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>10.1530/EC-18-0515</t>
+          <t>10.1159/000064764</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>Экспертный обзор</t>
+          <t>обзор (описательный)</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст</t>
+          <t>исправлено</t>
         </is>
       </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>"all these considerations are valid only if the hormonal examinations are performed before or atleast 4 h after the daily intake of LT4 and are carried out in the same laboratory"</t>
+          <t>Direct effects at the growth plate include the suppression of multiple gene expression, chondrocyte proliferation and matrix proteoglycan synthesis, sulfation, release and mineralization as well as the augmentation of hypertrophic cell apoptosis.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>доп_S2</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>S2.7</t>
+          <t>M3.4</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>У детей с центральным гипотиреозом св. Т4 на лечении держат в пределах возрастной нормы, целясь выше её медианы (уточняет 13.4b; для новорождённых см. 13.4c). Слайд 13: «верхняя половина возрастной нормы».</t>
+          <t>К частым проявлениям синдрома Кушинга у детей относится задержка полового развития.</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Persani L et al. Endocr Connect 2019;8(2):R44–R54</t>
+          <t>Stratakis CA. Endocrinol Metab Clin North Am 2012;41:793–803</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>30645189</t>
+          <t>23099271</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>10.1530/EC-18-0515</t>
+          <t>10.1016/j.ecl.2012.08.002</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>Экспертный обзор</t>
+          <t>обзор (описательный, педиатрия)</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст</t>
+          <t>частично</t>
         </is>
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>"pediatric patients should be monitored in order to maintain FT4 levels in the reference ranges for age" и "targeting this parameter above the median values of the reference range"</t>
+          <t>Other common problems reported in children include facial plethora, headaches, hypertension, hirsutism, amenorrhea, and delayed sexual development.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>доп_S2</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>S2.8</t>
+          <t>M3.5</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>При диагнозе центрального гипотиреоза надо учитывать и исключать помехи в определении св. Т4 и ТТГ; при подозрении на помеху в св. Т4 переходят на двухэтапный метод или масс-спектрометрию. Слайд 13, одна фраза в заметках без цифр (решение по слайду 13).</t>
+          <t>У кроликов после отмены дексаметазона возникал догоняющий рост, а возрастное «старение» зоны роста было отсрочено; авторы считают, что догоняющий рост отчасти объясняется этой задержкой старения.</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Persani L et al. Endocr Connect 2019;8(2):R44–R54</t>
+          <t>Gafni RI et al. Pediatr Res 2001;50:618–23</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>30645189</t>
+          <t>11641457</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr">
         <is>
-          <t>10.1530/EC-18-0515</t>
+          <t>10.1203/00006450-200111000-00014</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>Экспертный обзор</t>
+          <t>опыты на кроликах (экспериментальное исследование)</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст</t>
+          <t>исправлено</t>
         </is>
       </c>
       <c r="I245" s="2" t="inlineStr">
         <is>
-          <t>"the presence of a possible interference in FT4 or TSH measurement should also be considered and excluded" и "In case of a suspected FT4 assay interference, a 'two-step' method or a mass spectrometry should be considered"</t>
+          <t>These findings support our model that linear catch-up growth is caused, at least in part, by a delay in growth plate senescence.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>доп_S2</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>S2.9</t>
+          <t>M4.1</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>При преимущественно гипоталамическом поражении ТТГ бывает слегка повышен, как при субклиническом первичном гипотиреозе, но молекула лишена полной биологической активности, а св. Т4 уже низкий. Подтверждает механизм из 13.2a по вторичному источнику. Слайд 13, заметки.</t>
+          <t>У мальчиков большая часть эстрогенов (около 80 %) образуется вне яичек: фермент ароматаза превращает тестостерон и андростендион в эстрогены. Именно эстроген, а не андроген, служит ключевым половым гормоном пубертатного ускорения роста у мальчиков. По данным обзора, он, вероятно, главный гормон скачка роста и у девочек.</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Persani L et al. Endocr Connect 2019;8(2):R44–R54</t>
+          <t>Grumbach MM. J Pediatr Endocrinol Metab 2000;13 Suppl 6:1439-55</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>30645189</t>
+          <t>11202221</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>10.1530/EC-18-0515</t>
+          <t>10.1515/jpem-2000-s619</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>Экспертный обзор</t>
+          <t>обзор</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст</t>
+          <t>исправлено</t>
         </is>
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>"TSH levels are superimposable to those generally found in subclinical or mild primary hypothyroidism, although the molecule is devoid of full biological activity and the FT4 is already in the hypothyroid range"</t>
+          <t>in the male, estrogen (not androgen) derived from direct testicular secretion (approximately 20%) and from extragonadal aromatization of testosterone and androstenedione (approximately 80%), is the critical sex hormone in the pubertal growth spurt</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>доп_S2</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>S2.10</t>
+          <t>M4.2</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Центральный гипотиреоз, открывшийся на СТГ или половых стероидах, относится к картине дефицита нескольких гормонов гипофиза (дополняет 14.1b). Слайд 14, строка-ссылка по решению.</t>
+          <t>По данным обзора, эстрогены, вероятно, усиливают секрецию СТГ и тем самым повышают ИФР-1, а ИФР-1 стимулирует рост. Данные обзора: блокада рецепторов эстрогена снижает выработку СТГ, а ингибиторы ароматазы снижают ИФР-1 у здоровых мужчин.</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Persani L et al. Endocr Connect 2019;8(2):R44–R54</t>
+          <t>Juul A. Hum Reprod Update 2001;7:303-13</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>30645189</t>
+          <t>11392377</t>
         </is>
       </c>
       <c r="F247" s="2" t="inlineStr">
         <is>
-          <t>10.1530/EC-18-0515</t>
+          <t>10.1093/humupd/7.3.303</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>Экспертный обзор</t>
+          <t>обзор</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация и полный текст</t>
+          <t>исправлено</t>
         </is>
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>"The clinical management of CeH is further complicated by the combination with multiple pituitary deficiencies, as the introduction of sex steroids or GH replacements may uncover latent forms of CeH or increase the thyroxine requirements."</t>
+          <t>Taken together, these findings suggest that oestrogens may, in addition to their direct effects, stimulate GH secretion and thereby increase circulating IGF-I, which in turn may stimulate growth.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>доп_S2</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>S2.11</t>
+          <t>M4.3</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>В консенсусе по врождённому гипотиреозу отдельной стартовой дозы для св. Т4 от 5 до 10 пмоль/л нет: названы тяжёлая форма (&lt; 5 пмоль/л, 10–15), лёгкая (&gt; 10 пмоль/л, около 10) и норма до лечения (возможно 5–10) при общем потолке 15 мкг/кг/сут (уточняет 15.1). Слайд 15, заметки.</t>
+          <t>В опытах на молодых самках кроликов с удалёнными яичниками эстрадиол ускорял «старение» зоны роста: снижались скорость роста голени, деление хондроцитов, высота зоны роста и число клеток. Зона роста закрывалась раньше, когда деление хондроцитов приближалось к нулю. Авторы делают вывод, что эстроген не запускает окостенение напрямую, а приближает истощение способности хондроцитов делиться и тем самым более раннее закрытие зоны роста.</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>van Trotsenburg P et al. Thyroid 2021;31(3):387–419</t>
+          <t>Weise M, De-Levi S, Barnes KM, Gafni RI, Abad V, Baron J. Proc Natl Acad Sci USA 2001;98:6871-6</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>33272083</t>
+          <t>11381135</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
-          <t>10.1089/thy.2020.0333</t>
+          <t>10.1073/pnas.121180498</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>Раздел 3.1; 1/++0</t>
+          <t>опыты на кроликах (молодые самки после удаления яичников, эстрадиол в мышцу раз в неделю)</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст (PMC8001676; промежуточной категории нет)</t>
+          <t>исправлено</t>
         </is>
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>"Infants with mild CH (fT4 &gt; 10 pmol/L in combination with elevated TSH) should be treated with the lowest initial dose (∼10 μg/kg per day)"</t>
+          <t>estrogen does not induce growth plate ossification directly; instead, estrogen accelerates the programmed senescence of the growth plate, thus causing earlier proliferative exhaustion and consequently earlier fusion.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>доп_S2</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>S2.12</t>
+          <t>M4.4</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Национальное обследование Узбекистана: адекватно йодированная соль (&gt; 15 ppm) только в 36 % из 3413 домохозяйств; медиана йода в моче у небеременных некормящих женщин 140,9 мкг/л — йода достаточно; у беременных и кормящих — пограничная обеспеченность. Данные о женщинах, не о детях. Слайд 8, заметки.</t>
+          <t>У мужчины с нечувствительностью к эстрогенам (мутация гена рецептора эстрогена) зоны роста закрылись не полностью (рост 204 см в 28 лет), и рост продолжался во взрослом возрасте. У мужчин с дефицитом ароматазы рост тоже продолжается во взрослом возрасте из-за отсутствия слияния зон роста (по обзору); у описанного брата в 24 года рост был 204 см, а костный возраст — 14 лет.</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Rohner F, Nizamov F, Petry N, et al. Thyroid 2020;30(6):898–907</t>
+          <t>Smith EP et al. N Engl J Med 1994;331:1056-61; Morishima A et al. J Clin Endocrinol Metab 1995;80:3689-98</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>32098586</t>
+          <t>8090165; 8530621</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>10.1089/thy.2019.0788</t>
+          <t>10.1056/NEJM199410203311604; 10.1210/jcem.80.12.8530621</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>Поперечное популяционное обследование, 3413 домохозяйств</t>
+          <t>описания клинических случаев (один мужчина с мутацией рецептора эстрогена; брат и сестра с дефицитом ароматазы); для обобщения использован обзор Juul 2001</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация</t>
+          <t>подтверждено</t>
         </is>
       </c>
       <c r="I249" s="2" t="inlineStr">
         <is>
-          <t>"Overall, 36% of 3413 households had adequately iodized salt" … "The median urinary iodine concentration (UIC) of 140.9 μg/L … in nonpregnant nonlactating women indicated adequate iodine status"</t>
+          <t>The patient was tall (204 cm [80.3 in.]) and had incomplete epiphyseal closure, with a history of continued linear growth into adulthood despite otherwise normal pubertal development.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>доп_S2</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>S2.13</t>
+          <t>M5.1</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Исправление к 12.1: дизайн Cerbone 2011 — поперечное (cross-sectional) контролируемое исследование, а не «перекрёстное»; детей до включения наблюдали в среднем 3,3 года. Слайд 12. В файле A строку 12.1 поправить при сведении.</t>
+          <t>Ген SHOX находится в псевдоаутосомной области 1 на коротких плечах X- и Y-хромосом. Гены этой области не подвергаются инактивации X-хромосомы, поэтому у здорового человека работают обе копии, и для нормальной функции нужны обе.</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Cerbone M et al. Eur J Endocrinol 2011;164(4):591–7</t>
+          <t>Marchini A, Ogata T, Rappold GA. Endocr Rev, 2016;37:417–48 (расположение гена дополнительно: Rao E et al. Nat Genet, 1997;16:54–63)</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>21292920</t>
+          <t>27355317</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>10.1530/EJE-10-0979</t>
+          <t>10.1210/er.2016-1036</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>Поперечное контролируемое исследование, n = 36 + 36 контролей</t>
+          <t>обзор (Endocrine Reviews), данные у человека</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>исправлено: аннотация</t>
+          <t>подтверждено</t>
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>"The aim of this cross-sectional, controlled study was to evaluate growth and intellectual outcome in children with persistent SH who have never been treated with levothyroxine."</t>
+          <t>Genes residing in this region escape X inactivation (the process by which one of the X chromosomes is rendered genetically silent), and therefore two active copies of the genes are required for normal physiological function.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>доп_S3</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>S3.01</t>
+          <t>M5.2</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Консенсус Общества гипофиза, раздел о детях: отсутствие прибавки роста при прибавке массы — самое частое проявление синдрома Кушинга у детей; поэтому у детей болезнь заметить несколько проще, чем у подростков после пубертата и у взрослых. Слайд 16, заметки.</t>
+          <t>При синдроме Тернера остаётся одна копия гена SHOX вместо двух. По международным рекомендациям 2024 года именно недостаток SHOX — главная причина низкорослости и скелетных изменений; свой вклад вносят также нарушения оси СТГ — ИФР-1 (включая нечувствительность к ИФР-1) и нехватка эстрогенов.</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Fleseriu M, Auchus R, Bancos I et al. Lancet Diabetes Endocrinol 2021;9(12):847–875</t>
+          <t>Gravholt CH et al. Eur J Endocrinol, 2024;190:G53–G151 (дополнительно: Marchini A et al. Endocr Rev, 2016;37:417–48)</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>34687601</t>
+          <t>38748847</t>
         </is>
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
-          <t>10.1016/S2213-8587(21)00235-7</t>
+          <t>10.1093/ejendo/lvae050</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>Консенсус экспертов (Pituitary Society); раздел о детях без градации</t>
+          <t>клиническое руководство ESE/PES (консенсус с системным поиском по GRADE)</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст (PMC8743006)</t>
+          <t>подтверждено</t>
         </is>
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>"Lack of height gain concomitant with weight gain is the most common CS presentation in children, making the disorder somewhat easier to detect compared with post-pubertal adolescents or adults."</t>
+          <t>in the pseudo-autosomal regions of the X chromosome is primarily responsible for the short stature and skeletal dysplasia in TS. However, perturbations in GH and insulin-like growth factor-I (IGF-I) physiology, including resistance to IGF-I, and estrogen deficiency may also contribute to impaired linear growth.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>доп_S3</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>S3.02</t>
+          <t>M5.3</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>То же по обзору протокола NIH: самый частый первый симптом — прибавка массы; у детей самое частое проявление — рост, не прибавляющий вместе с массой. Слайд 16, заметки (поддержка S3.01).</t>
+          <t>Ген SHOX работает в хондроцитах зоны роста человека, больше всего в созревших (гипертрофированных) хондроцитах. В зародыше он сильнее всего выражен в средней части конечностей (локоть, колено, кости предплечья и голени), и именно предплечья и голени страдают при его дефиците.</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Stratakis CA. Endocrinol Metab Clin North Am 2012;41(4):793–803</t>
+          <t>Marchini A, Ogata T, Rappold GA. Endocr Rev, 2016;37:417–48 (дополнительно: Gravholt CH et al. Eur J Endocrinol, 2024;190:G53–G151; Clement-Jones M et al. Hum Mol Genet, 2000;9:695–702)</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>23099271</t>
+          <t>27355317</t>
         </is>
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.ecl.2012.08.002</t>
+          <t>10.1210/er.2016-1036</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>Нарративный обзор</t>
+          <t>обзор (Endocrine Reviews); данные на тканях человека (зародыши, срезы зоны роста) и клиническое руководство</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст (PMC3594781)</t>
+          <t>частично</t>
         </is>
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>"The most common presenting symptom is weight gain; in childhood, lack of height gain consistent with the weight gain is the most common presentation of Cushing syndrome."</t>
+          <t>SHOX was detected in the growth plate, particularly in terminally differentiated hypertrophic chondrocytes and, to a lesser extent, in chondrocytes of the resting and proliferative zones.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>доп_S3</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>S3.03</t>
+          <t>M5.4</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Японская ретроспективная серия: 19 детей с болезнью Кушинга (≤ 18 лет; 1994–2025, один центр; медиана возраста при диагнозе 13 лет, 6–17; 12 девочек). Рост в СО в среднем −0,45 в начале симптомов и −2,0 к диагнозу; ИМТ в СО +0,61 и +1,6. Прибавка массы со снижением скорости роста у 88,9 %. Медиана срока до диагноза 2,7 года (0,25–5,8). Слайд 16, заметки.</t>
+          <t>Скелетные признаки при синдроме Тернера встречаются реже, чем низкорослость и недостаточность яичников: короткая IV пястная кость, вальгусное отклонение предплечья в локте, деформация Маделунга (по данным обзора, лишь около 7,5 % случаев), высокое нёбо. Описаны также искривления позвоночника и вальгусная деформация коленей.</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Yamamoto M, Mukoyama Y, Kishi K et al. Endocr J 2026 (онлайн 02.07.2026; том и страницы в записи PubMed не указаны)</t>
+          <t>Marchini A, Ogata T, Rappold GA. Endocr Rev, 2016;37:417–48 (дополнительно: Gravholt CH et al. Eur J Endocrinol, 2024;190:G53–G151)</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>42386546</t>
+          <t>27355317</t>
         </is>
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
-          <t>10.1507/endocrj.EJ26-0212</t>
+          <t>10.1210/er.2016-1036</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>Ретроспективная серия, один центр, n = 19</t>
+          <t>обзор (Endocrine Reviews) и клиническое руководство</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация</t>
+          <t>подтверждено</t>
         </is>
       </c>
       <c r="I253" s="2" t="inlineStr">
         <is>
-          <t>"The mean standard deviation scores (SDS) (SD) of height and body mass index (BMI) at onset and diagnosis were -0.45 (0.63) and -2.0 (1.1), and 0.61 (0.95) and 1.6 (0.75)" … "Median time to diagnosis was 2.7 (0.25-5.8) years."</t>
+          <t>Skeletal defects, which appear less frequently, include short fourth metacarpals (C), cubitus valgus (forearm angled away from the body), micrognathia, Madelung deformity, high-arched palate, webbed neck, broad chest, and low-set ears</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>доп_S3</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>S3.04</t>
+          <t>M5.5</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Совет «ингаляционный глюкокортикоид ради роста не отменять, подбирать минимальную эффективную дозу» в аннотации кокрейновского обзора отсутствует. Аннотация говорит только, что торможение роста максимально в первый год и слабее в последующие. На слайд не ставится; в заметках слайда 18 — мнение лектора без ссылки на данные (решение по слайду 18).</t>
+          <t>Без лечения гормоном роста взрослый рост женщин с синдромом Тернера в среднем 138–147 см (по странам), то есть примерно на 20 см (около 3 стандартных отклонений) ниже среднего роста в популяции во многих странах.</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Zhang L, Prietsch SO, Ducharme FM. Cochrane Database Syst Rev 2014;(7):CD009471</t>
+          <t>Gravholt CH et al. Eur J Endocrinol, 2024;190:G53–G151</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>25030198</t>
+          <t>38748847</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t>10.1002/14651858.CD009471.pub2</t>
+          <t>10.1093/ejendo/lvae050</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>Кокрейновский систематический обзор, 25 РКИ</t>
+          <t>клиническое руководство ESE/PES (консенсус с системным поиском по GRADE)</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>не подтверждено (в аннотации нет; полный текст не в списке доступных)</t>
+          <t>подтверждено</t>
         </is>
       </c>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>Аннотация, вывод: "ICS-induced growth suppression seems to be maximal during the first year of therapy and less pronounced in subsequent years of treatment." О дозе как мере защиты роста не сказано.</t>
+          <t>resulting in an average adult height ranging from 138 to 147 cm, depending on the country; this represents a deficit of ∼20 cm (−3 SD) compared with population means for many countries.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>доп_S3</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>S3.05</t>
+          <t>M5.6</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>Риск надпочечниковой недостаточности при отмене системных глюкокортикоидов после длительного приёма. В обоих полных текстах отмена экзогенных глюкокортикоидов не обсуждается: надпочечниковая недостаточность описана только после операции, при медикаментозном лечении и после адреналэктомии. На слайд 17 не ставится; в заметках — совет лектора (решение по слайду 17).</t>
+          <t>Недостаточность яичников добавляет потерю роста: пубертатный скачок роста, который зависит от эстрогенов, у девочек с синдромом Тернера минимален или отсутствует. Нехватка эстрогенов может вносить вклад в низкорослость, но главная причина — недостаток SHOX.</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Stratakis CA. Endocrinol Metab Clin North Am 2012;41(4):793–803; Fleseriu M et al. Lancet Diabetes Endocrinol 2021;9(12):847–875</t>
+          <t>Gravholt CH et al. Eur J Endocrinol, 2024;190:G53–G151</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>23099271; 34687601</t>
+          <t>38748847</t>
         </is>
       </c>
       <c r="F255" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.ecl.2012.08.002; 10.1016/S2213-8587(21)00235-7</t>
+          <t>10.1093/ejendo/lvae050</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Нарративный обзор; консенсус экспертов</t>
+          <t>клиническое руководство ESE/PES (консенсус с системным поиском по GRADE)</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>не подтверждено (в полных текстах нет)</t>
+          <t>исправлено</t>
         </is>
       </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>Нет цитаты: поиск по "withdraw", "taper", "exogenous", "adrenal insufficiency" в обоих полных текстах; об экзогенных глюкокортикоидах у Stratakis только "chronic administration of glucocorticoids or ACTH" как причина.</t>
+          <t>Linear growth remains suboptimal in childhood and the estrogen-mediated pubertal growth spurt is minimal or absent</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>доп_S3</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>S3.06</t>
+          <t>M6.1</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Опухоль коры надпочечника у малышей, выделяющая андрогены, при которой рост может не замедляться. В полном тексте Stratakis 2012 связи опухоли коры с андрогенами и сохранённым ростом нет; о вирилизации сказано только в общем перечне симптомов у детей в пубертате. На слайд 19 не ставится (решение по слайду 19).</t>
+          <t>ИФР-1 как гормон вырабатывается главным образом в печени, и его выработка регулируется СТГ.</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Stratakis CA. Endocrinol Metab Clin North Am 2012;41(4):793–803</t>
+          <t>Fazeli PK, Klibanski A. J Endocrinol 2014;220:R57–65</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>23099271</t>
+          <t>24363451</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.ecl.2012.08.002</t>
+          <t>10.1530/JOE-13-0477</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Нарративный обзор</t>
+          <t>обзор (с опорой на опыты на мышах)</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>не подтверждено (в полном тексте нет)</t>
+          <t>подтверждено</t>
         </is>
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>Единственное упоминание: "Pubertal children may present with virilization." Об андрогенах опухолей коры и росте при них не сказано.</t>
+          <t>Insulin-like growth factor (IGF)-I is a hormone produced primarily by the liver and regulated by growth hormone (GH) secretion by the somatotroph cells of the anterior pituitary gland.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>доп_S3</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>S3.07</t>
+          <t>M6.2</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>Полуночный кортизол сыворотки (&gt; 4,4 мкг/дл) в протоколе NIH берут после подтверждённого повышения суточного кортизола мочи (3 сбора); для точности суточный профиль требует госпитализации, что ограничивает его как рутинный скрининг. Слайд 20, таблица («в стационаре, после повышенного кортизола мочи») и заметки.</t>
+          <t>При недостаточном питании (общий дефицит энергии, белково-энергетическая недостаточность, нервная анорексия) развивается приобретённая резистентность к СТГ: СТГ в крови повышен, а ИФР-1 снижен.</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Stratakis CA. Endocrinol Metab Clin North Am 2012;41(4):793–803</t>
+          <t>Fazeli PK, Klibanski A. J Endocrinol 2014;220:R57–65</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>23099271</t>
+          <t>24363451</t>
         </is>
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.ecl.2012.08.002</t>
+          <t>10.1530/JOE-13-0477</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Нарративный обзор (протокол NIH)</t>
+          <t>обзор</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст</t>
+          <t>подтверждено</t>
         </is>
       </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>"following confirmation of elevated 24-hour UFC (3 collections), a single midnight cortisol value of greater than 4.4 μg/dL" … "However, for accuracy, diurnal testing requires an inpatient stay, and this may limit its use as a routine screening test."</t>
+          <t>States of undernutrition are characterized by GH resistance. Decreased total energy intake, as well as isolated protein-calorie malnutrition and isolated nutrient deficiencies, result in elevated GH levels and low levels of IGF1.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>доп_S3</t>
+          <t>M_механизмы</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>S3.08</t>
+          <t>M6.3</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Малая двухдневная проба с дексаметазоном (30 мкг/кг на приём, не больше 0,5 мг, каждые 6 ч, 8 доз) в протоколе NIH — первая часть классической пробы Лиддла, которую проводят для поиска причины: при неподавлении в большой ночной пробе, отрицательной визуализации или подозрении на поражение надпочечников; оценивают кортизол мочи и 17-гидроксикортикостероиды. Слайд 20, заметки («тест центра для поиска причины»).</t>
+          <t>При хроническом воспалении провоспалительные цитокины (вместе с глюкокортикоидами и недостаточным питанием) нарушают ось СТГ — ИФР-1 и напрямую действуют на зону роста, меняя развитие хряща и местные ростовые сигналы.</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Stratakis CA. Endocrinol Metab Clin North Am 2012;41(4):793–803</t>
+          <t>Wong SC et al. Endocr Rev 2016;37:62–110</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>23099271</t>
+          <t>26720129</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.ecl.2012.08.002</t>
+          <t>10.1210/er.2015-1026</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>Нарративный обзор (протокол NIH)</t>
+          <t>обзор</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст</t>
+          <t>частично</t>
         </is>
       </c>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>"Indications for obtaining the classic Liddle's test, low-dose dexamethasone (30 μg/kg/dose; maximum 0.5 mg/dose) every 6 hours for 8 doses … include nonsuppression of serum cortisol levels during the HDDST and/or negative imaging studies, and/or suspected adrenal disease."</t>
+          <t>These factors can impair growth by their effects on the GH-IGF axis and also directly at the level of the growth plate via alterations in chondrogenesis and local growth factor signaling.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>доп_S3</t>
+          <t>доп_S1</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>S3.09</t>
+          <t>S1.01</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>Суточную мочу у детей амбулаторно часто трудно собрать надёжно. Ложно высокий свободный кортизол мочи: в том числе при тяжёлом хроническом ожирении и большом объёме выпитой жидкости; ложно низкий — в основном при неполном сборе. Уточняет 21.1b (ожирение «тяжёлое хроническое», «высокий водный режим» теперь подтверждён полным текстом). Слайд 21, таблица и заметки.</t>
+          <t>Британский консенсус по аденомам гипофиза у детей (части 1 и 2) разработала многопрофильная группа экспертов в 2014–2022 годах с международной Дельфи-панелью; 74 рекомендации для детей и молодых людей до 19 лет, в части 1 их 17. Общества-издатели в аннотации не названы. Слайд 4, заметки.</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Stratakis CA. Endocrinol Metab Clin North Am 2012;41(4):793–803</t>
+          <t>Korbonits M, Blair JC, Boguslawska A et al. Nat Rev Endocrinol 2024;20(5):278–289 (часть 1)</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>23099271</t>
+          <t>38336897</t>
         </is>
       </c>
       <c r="F259" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.ecl.2012.08.002</t>
+          <t>10.1038/s41574-023-00948-8</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>Нарративный обзор</t>
+          <t>Консенсус-руководство (поиск литературы и Дельфи)</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст</t>
+          <t>подтверждено: аннотация</t>
         </is>
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>"it is often difficult to obtain a 24-hour urine collection reliably in the outpatient setting, particularly in the pediatric population" … "chronic and severe obesity … and high water intake" … "falsely low UFC may be obtained mostly with inadequate collection."</t>
+          <t>"a multidisciplinary expert group systematically developed the first comprehensive clinical practice consensus guideline for children and young people under the age 19 years … international Delphi consensus panel of experts … consolidated into 74 recommendations"</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>доп_S3</t>
+          <t>доп_S1</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>S3.10</t>
+          <t>S1.02</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Подтверждённая прибавка роста — простой способ отличить ребёнка с псевдо-Кушингом от ребёнка с синдромом Кушинга. Слайд 21, заметки.</t>
+          <t>В систематическом обзоре 28 работ определяли низкорослость как рост ниже −2 СО, 19 работ брали процентильный порог (в основном 3-й центиль); 8 работ использовали оба определения, 3 работы определения не давали. Слайд 6, тело (строка 4) и заметки.</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Stratakis CA. Endocrinol Metab Clin North Am 2012;41(4):793–803</t>
+          <t>Mameli C et al. Ital J Pediatr 2026;52(1)</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>23099271</t>
+          <t>41723458</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.ecl.2012.08.002</t>
+          <t>10.1186/s13052-026-02215-8</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>Нарративный обзор (мнение автора)</t>
+          <t>Систематический обзор (PRISMA 2020; 35 клинических и 7 биохимических работ)</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст</t>
+          <t>подтверждено: аннотация</t>
         </is>
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>"Confirmed height gain is a simple way to help distinguish children with pseudo-Cushing from those with Cushing syndrome."</t>
+          <t>"28 studies used a threshold of &lt; 2 standard deviation score, while 19 applied percentile-based cut-offs (mostly the 3rd percentile); 8 studies considered both definitions, 3 studies do not report any definition."</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>доп_S3</t>
+          <t>доп_S1</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>S3.11</t>
+          <t>S1.03</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>У 5–10 % больных секреция кортизола периодическая, и ночная проба с 1 мг дексаметазона и суточный кортизол мочи могут быть нормальными; при подозрении на периодический синдром Кушинга советуют продолжать наблюдение, включая рост и суточный кортизол мочи. Слайд 21, заметки.</t>
+          <t>В работах обзора скорость роста и целевой рост использовали редко, хотя у них есть диагностическая ценность. Слайд 6, заметки.</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Stratakis CA. Endocrinol Metab Clin North Am 2012;41(4):793–803</t>
+          <t>Mameli C et al. Ital J Pediatr 2026;52(1)</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>23099271</t>
+          <t>41723458</t>
         </is>
       </c>
       <c r="F261" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.ecl.2012.08.002</t>
+          <t>10.1186/s13052-026-02215-8</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>Нарративный обзор</t>
+          <t>Систематический обзор</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст</t>
+          <t>подтверждено: аннотация</t>
         </is>
       </c>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>"5% to 10% of patients may have intermittent or periodic cortisol hypersecretion and may not manifest abnormal results to either test. If periodic or intermittent Cushing syndrome is suspected, continuous follow-up … including monitoring of growth and 24-hour UFC."</t>
+          <t>"Growth velocity and target height were rarely used, despite their diagnostic value."</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>доп_S3</t>
+          <t>доп_S1</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>S3.12</t>
+          <t>S1.04</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Ночная проба с дексаметазоном может быть ненадёжной у женщин, принимающих эстрогены внутрь (рекомендация для взрослых). Слайд 21, заметки (вывод лектора: девушке на эстрогенах начинать с мочи или слюны).</t>
+          <t>В работах обзора пользовались местными нормами роста, где они были; иначе чаще всего нормами ВОЗ и CDC. Какие нормы выбрать в Узбекистане и СНГ, обзор не говорит. Слайд 6, заметки.</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Fleseriu M et al. Lancet Diabetes Endocrinol 2021;9(12):847–875</t>
+          <t>Mameli C et al. Ital J Pediatr 2026;52(1)</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>34687601</t>
+          <t>41723458</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>10.1016/S2213-8587(21)00235-7</t>
+          <t>10.1186/s13052-026-02215-8</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>Консенсус экспертов; HQ, SR (высокое качество, сильная)</t>
+          <t>Систематический обзор; описание практики, не рекомендация</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст</t>
+          <t>подтверждено: аннотация</t>
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>"DST may be the preferred test for shift workers and patients with disrupted circadian rhythm due to uneven sleep schedules, but may not be reliable in women treated with oral estrogen (HQ, SR)."</t>
+          <t>"Local growth charts were employed when available; otherwise, WHO and CDC references were most used."</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>доп_S3</t>
+          <t>доп_S1</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>S3.13</t>
+          <t>S1.05</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Раздел о детях: после успешного лечения функция надпочечников обычно восстанавливается примерно за 12 мес. Слайд 23, тело.</t>
+          <t>Уточнение к 07.1a. Аннотация Martin 2011 прямо говорит об отставании костного возраста только у здоровых низкорослых детей. О дефиците СТГ сказано лишь, что на лечении СТГ костный возраст догоняет; «отстаёт при дефиците СТГ» — вывод, а не цитата. На слайде 7 оставлены только здоровые низкорослые дети.</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Fleseriu M et al. Lancet Diabetes Endocrinol 2021;9(12):847–875</t>
+          <t>Martin DD, Wit JM, Hochberg Z et al. Horm Res Paediatr 2011;76(1):1–9 (часть 1)</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>34687601</t>
+          <t>21691054</t>
         </is>
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
-          <t>10.1016/S2213-8587(21)00235-7</t>
+          <t>10.1159/000329372</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>Консенсус экспертов; раздел о детях без градации</t>
+          <t>Нарративный обзор</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст</t>
+          <t>исправлено (часть о дефиците СТГ со слайда снята)</t>
         </is>
       </c>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>"With successful treatment, adrenal function typically recovers within approximately 12 months."</t>
+          <t>"Healthy tall children tend to have advanced BA and healthy short children tend to have delayed BA in comparison to chronological age. Growth hormone (GH) treatment of children with GH deficiency leads to a catch-up in BA"</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>доп_S3</t>
+          <t>доп_S1</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>S3.14</t>
+          <t>S1.06</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Больным в ремиссии после операции нужна заместительная терапия глюкокортикоидами до восстановления оси гипоталамус — гипофиз — надпочечники (общий раздел, без градации). Слайд 23, тело.</t>
+          <t>Arlien-Søborg 2025 — Дельфи-опрос по диагностике дефицита СТГ у детей и взрослых, начатый членами Общества по изучению гормона роста (GRS). Атрибуция ячейки таблицы слайда 4; содержание опроса — 38.2.</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Fleseriu M et al. Lancet Diabetes Endocrinol 2021;9(12):847–875</t>
+          <t>Arlien-Søborg MC, Radovick S, Boguszewski MCS et al. Pituitary 2025;28(3):57</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>34687601</t>
+          <t>40335774</t>
         </is>
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>10.1016/S2213-8587(21)00235-7</t>
+          <t>10.1007/s11102-025-01526-z</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>Консенсус экспертов; раздел «Background», без градации</t>
+          <t>Дельфи-опрос (педиатры n = 18, эндокринологи взрослых n = 25, 14 стран)</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст</t>
+          <t>подтверждено: аннотация</t>
         </is>
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>"Patients in remission require GC replacement until HPA axis recovery."</t>
+          <t>"The Growth Hormone Research Society members initiated a Delphi survey of the diagnosis of GHD in children and adults."</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>доп_S3</t>
+          <t>доп_S2</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>S3.15</t>
+          <t>S2.1a</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>После успешной операции при болезни Кушинга или удаления аденомы надпочечника наступает период надпочечниковой недостаточности до восстановления оси; сразу после операции — стрессовые дозы с быстрым снижением до физиологической (12–15 мг/м² в сутки в 2–3 приёма); стрессовые дозы при острой болезни, травме и операции нужны и при временной, и при постоянной недостаточности. Слайд 23, тело и заметки.</t>
+          <t>Ретроспективная когорта 111 детей с лёгким субклиническим гипотиреозом (ТТГ 5–10 мЕд/л минимум дважды, наблюдение ≥ 6 мес; идиопатические и с сопутствующими причинами): рост оставался в норме и у нелеченых не ухудшился; при идиопатической форме левотироксин понадобился 8,6 %. Всего: эутиреоз у 45 (40,5 %), стойкий субклинический у 49 (44,2 %), лечение у 17 (15,3 %). Слайд 12.</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Stratakis CA. Endocrinol Metab Clin North Am 2012;41(4):793–803</t>
+          <t>Zengin NŞ, Sağsak E, Geylani Güleç S. J Clin Res Pediatr Endocrinol 2026;18(3):498–507</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>23099271</t>
+          <t>41914440</t>
         </is>
       </c>
       <c r="F265" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.ecl.2012.08.002</t>
+          <t>10.4274/jcrpe.galenos.2026.2025-9-27</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>Нарративный обзор</t>
+          <t>Ретроспективная когорта, n = 111</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст</t>
+          <t>подтверждено: аннотация</t>
         </is>
       </c>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>"After the completion of successful TSS in Cushing disease … there will be a period of adrenal insufficiency while the hypothalamic pituitary adrenal axis is recovering." … "stress dosing for acute illness, trauma, or surgical procedures is required for both temporary and permanent adrenal insufficiency."</t>
+          <t>"Idiopathic cases showed the most favorable course, with only 8.6% requiring therapy." … "Growth parameters remained within normal limits, with no deterioration in untreated children."</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>доп_S3</t>
+          <t>доп_S2</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>S3.16</t>
+          <t>S2.1b</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Пожизненное наблюдение за рецидивом болезни Кушинга (рекомендация для взрослых). Слайд 23, тело.</t>
+          <t>В той же когорте тиреоидит Хашимото — сильнейший предиктор прогрессии: левотироксин понадобился 42,1 % против 9,8 % без тиреоидита; ТТГ исходно &gt; 7,5 мЕд/л повышал вероятность лечения примерно в 3,5 раза. Слайд 12, заметки.</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Fleseriu M et al. Lancet Diabetes Endocrinol 2021;9(12):847–875</t>
+          <t>Zengin NŞ et al. J Clin Res Pediatr Endocrinol 2026;18(3):498–507</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>34687601</t>
+          <t>41914440</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>10.1016/S2213-8587(21)00235-7</t>
+          <t>10.4274/jcrpe.galenos.2026.2025-9-27</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>Консенсус экспертов; MQ, SR (умеренное качество, сильная)</t>
+          <t>Ретроспективная когорта, n = 111</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст</t>
+          <t>подтверждено: аннотация</t>
         </is>
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>"We recommend lifelong monitoring for recurrence of CD (MQ, SR)."</t>
+          <t>"Hashimoto's thyroiditis (HT) was the strongest predictor of progression (42.1% vs. 9.8% in non-HT). A baseline TSH&gt;7.5 mIU/L increased treatment likelihood by ~3.5-fold."</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>доп_S3</t>
+          <t>доп_S2</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>S3.17</t>
+          <t>S2.2</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>После лучевой терапии пожизненно наблюдают и за дефицитом гормонов гипофиза, и за рецидивом (рекомендация для взрослых). Слайд 23, тело.</t>
+          <t>Среди семи авторов обзора Salerno 2026 (источник доз левотироксина на слайде 10) есть сотрудник отдела медицинских вопросов фармацевтической компании (Centonze C). У двух других авторов та же строка приклеена к университетской аффилиации, вероятно, артефакт разбора. Что компания выпускает левотироксин, PubMed не сообщает, на слайд и в заметки не ставится. Слайд 10, заметки.</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Fleseriu M et al. Lancet Diabetes Endocrinol 2021;9(12):847–875</t>
+          <t>Salerno M et al. Front Endocrinol (Lausanne) 2026;16:1744280</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>34687601</t>
+          <t>41585793</t>
         </is>
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
-          <t>10.1016/S2213-8587(21)00235-7</t>
+          <t>10.3389/fendo.2025.1744280</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>Консенсус экспертов; HQ, SR (высокое качество, сильная)</t>
+          <t>Аффилиация автора в записи PubMed</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст</t>
+          <t>подтверждено: запись PubMed</t>
         </is>
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>"Lifelong monitoring for pituitary hormone deficiencies and recurrence is required in all patients undergoing RT (HQ, SR)."</t>
+          <t>Centonze C: "Medical Affairs, Merck Serono SpA, Rome, Italy."</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>доп_S3</t>
+          <t>доп_S2</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>S3.18</t>
+          <t>S2.3</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Частота рецидива после успешной операции в публикациях 5–35 %; половина рецидивов в первые 5 лет, половина позже, вплоть до 10 лет и более (данные о взрослых). Слайд 23, заметки.</t>
+          <t>Приобретённый центральный гипотиреоз связан в основном с объёмными образованиями гипоталамо-гипофизарной области; у детей самое частое такое образование — краниофарингиома. Слайд 13.</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Fleseriu M et al. Lancet Diabetes Endocrinol 2021;9(12):847–875</t>
+          <t>Persani L, Cangiano B, Bonomi M. Endocr Connect 2019;8(2):R44–R54</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>34687601</t>
+          <t>30645189</t>
         </is>
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>10.1016/S2213-8587(21)00235-7</t>
+          <t>10.1530/EC-18-0515</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>Консенсус экспертов; обзор литературы («Background»)</t>
+          <t>Экспертный обзор</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст</t>
+          <t>подтверждено: полный текст (PMC6373625)</t>
         </is>
       </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>"Published recurrence rates vary between 5% and 35%, with half appearing within the first 5 years after surgery and half after up to 10 years or more."</t>
+          <t>"the acquired forms of CeH are mainly related to expansive lesions of the hypothalamic/pituitary region … Craniopharyngiomas represent the most prevalent expansive lesion associated with CeH in pediatric patients."</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>доп_S3</t>
+          <t>доп_S2</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>S3.19</t>
+          <t>S2.4</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>Общество гипофиза советует начинать с ночной пробы с дексаметазоном, суточного свободного кортизола мочи и/или кортизола слюны поздно вечером в зависимости от местной доступности; несколько проб слюны пациенту выполнить проще. Это проверенная часть цитаты из 20.1b (строка 20.1b в файле B помечена «не подтверждено» как утверждение об утреннем кортизоле). Слайд 20, тело, строка 1.</t>
+          <t>Такие образования обычно нарушают функцию и гипофиза, и гипоталамуса, давая картину дефицита нескольких гормонов гипофиза. Слайд 13 (строка о причинах), слайд 14 (строка-ссылка).</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Fleseriu M et al. Lancet Diabetes Endocrinol 2021;9(12):847–875</t>
+          <t>Persani L et al. Endocr Connect 2019;8(2):R44–R54</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>34687601</t>
+          <t>30645189</t>
         </is>
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t>10.1016/S2213-8587(21)00235-7</t>
+          <t>10.1530/EC-18-0515</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>Консенсус экспертов; HQ, SR (высокое качество, сильная)</t>
+          <t>Экспертный обзор</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -14072,91 +14755,91 @@
       </c>
       <c r="I269" s="2" t="inlineStr">
         <is>
-          <t>"We recommend starting with DST, UFC, and/or LNSC (HQ, SR) depending on local availability; multiple LNSCs may be easier for the patient to complete (HQ, SR)."</t>
+          <t>"these lesions usually affect both pituitary and hypothalamus function with a resulting MPHDs clinical picture"</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>доп_S4</t>
+          <t>доп_S2</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>S4.01</t>
+          <t>S2.5</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Авторы метаанализа о сдвиге телархе призывают пересмотреть определение преждевременного пубертата: традиционное определение может устареть. О пересмотре порогов задержки пубертата в аннотации не сказано. Слайд 25, заметки.</t>
+          <t>МРТ гипоталамо-гипофизарной области при впервые найденном центральном гипотиреозе.</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Eckert-Lind C et al., JAMA Pediatr, 2020;174(4):e195881</t>
+          <t>Persani 2019 (полный текст); Persani 2018 ETA (аннотация); van Trotsenburg 2021 (полный текст)</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>32040143</t>
+          <t>30645189; 30374425; 33272083</t>
         </is>
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
-          <t>10.1001/jamapediatrics.2019.5881</t>
+          <t>10.1530/EC-18-0515; 10.1159/000491388; 10.1089/thy.2020.0333</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>Систематический обзор и метаанализ, 30 исследований</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация</t>
+          <t>не подтверждено (в доступных текстах МРТ не названа; полный текст ETA 2018 недоступен)</t>
         </is>
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>"The medical community needs current and relevant data to redefine "precocious puberty," because the traditional definition may be outdated, at least in some regions of the world."</t>
+          <t>Нет цитаты: поиск "MRI", "magnetic", "imaging" в полных текстах; в van Trotsenburg "imaging" только о щитовидной железе.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>доп_S4</t>
+          <t>доп_S2</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>S4.02</t>
+          <t>S2.6</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>Изолированное лобковое и подмышечное оволосение зависит в основном от андрогенов надпочечников и не означает начала гонадотропин-зависимого пубертата; первый признак пубертата у мальчиков — увеличение яичек (объём больше 3 мл). Слайд 25, заметки.</t>
+          <t>Св. Т4 на лечении оценивают по крови, взятой до утренней дозы левотироксина или не раньше чем через 4 ч после неё, и в той же лаборатории. Слайд 13 (тело: «кровь до утренней таблетки»; заметки: 4 ч, та же лаборатория).</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Persani L et al., Endocrine, 2021;71(3):681–688</t>
+          <t>Persani L et al. Endocr Connect 2019;8(2):R44–R54</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>33512657</t>
+          <t>30645189</t>
         </is>
       </c>
       <c r="F271" s="2" t="inlineStr">
         <is>
-          <t>10.1007/s12020-021-02626-z</t>
+          <t>10.1530/EC-18-0515</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>Мнение экспертов Endo-ERN (обзор, не руководство)</t>
+          <t>Экспертный обзор</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
@@ -14166,44 +14849,44 @@
       </c>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>"The appearance of pubic and axillary hair is mainly dependent upon adrenal androgens and, if isolated, should not be interpreted as the beginning of gonadotrophin-dependent puberty"</t>
+          <t>"all these considerations are valid only if the hormonal examinations are performed before or atleast 4 h after the daily intake of LT4 and are carried out in the same laboratory"</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>доп_S4</t>
+          <t>доп_S2</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>S4.03</t>
+          <t>S2.7</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Если к 13 (девочки) или 14 (мальчики) годам признаков пубертата нет, первым шагом определяют гонадотропины и костный возраст; высокие гонадотропины указывают на первичный дефект гонад, и ключевой шаг — кариотип. Слайд 26, заметки.</t>
+          <t>У детей с центральным гипотиреозом св. Т4 на лечении держат в пределах возрастной нормы, целясь выше её медианы (уточняет 13.4b; для новорождённых см. 13.4c). Слайд 13: «верхняя половина возрастной нормы».</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Persani L et al., Endocrine, 2021;71(3):681–688</t>
+          <t>Persani L et al. Endocr Connect 2019;8(2):R44–R54</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>33512657</t>
+          <t>30645189</t>
         </is>
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t>10.1007/s12020-021-02626-z</t>
+          <t>10.1530/EC-18-0515</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>Мнение экспертов Endo-ERN (предложенный алгоритм)</t>
+          <t>Экспертный обзор</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -14213,44 +14896,44 @@
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>"the determination of gonadotropins and bone age can be useful as a first diagnostic approach. High gonadotropins point to a primary gonadal defect and karyotype is a key step for the definition of these cases."</t>
+          <t>"pediatric patients should be monitored in order to maintain FT4 levels in the reference ranges for age" и "targeting this parameter above the median values of the reference range"</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>доп_S4</t>
+          <t>доп_S2</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>S4.04</t>
+          <t>S2.8</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Мальчика с недоразвитым (на 2,5 СО и больше ниже среднего), но в остальном нормальным половым членом без гипоспадии обследуют на врождённый гипогонадотропный гипогонадизм: базальные гормоны оси в минипубертат (около 1–4 мес после рождения), позже — проба с ХГЧ. Слайд 27, заметки.</t>
+          <t>При диагнозе центрального гипотиреоза надо учитывать и исключать помехи в определении св. Т4 и ТТГ; при подозрении на помеху в св. Т4 переходят на двухэтапный метод или масс-спектрометрию. Слайд 13, одна фраза в заметках без цифр (решение по слайду 13).</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Persani L et al., Endocrine, 2021;71(3):681–688</t>
+          <t>Persani L et al. Endocr Connect 2019;8(2):R44–R54</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>33512657</t>
+          <t>30645189</t>
         </is>
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t>10.1007/s12020-021-02626-z</t>
+          <t>10.1530/EC-18-0515</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>Мнение экспертов Endo-ERN</t>
+          <t>Экспертный обзор</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -14260,44 +14943,44 @@
       </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>"should be further investigated to exclude CHH, based on baseline assessment of the HPG axis during minipuberty (~1–4 months after birth), or an HCG stimulation test thereafter"</t>
+          <t>"the presence of a possible interference in FT4 or TSH measurement should also be considered and excluded" и "In case of a suspected FT4 assay interference, a 'two-step' method or a mass spectrometry should be considered"</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>доп_S4</t>
+          <t>доп_S2</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>S4.05</t>
+          <t>S2.9</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Конституциональную задержку диагностируют только после исключения гипергонадотропного и врождённого гипогонадотропного гипогонадизма. Откладывать диагноз на поздний возраст не следует: это может снизить итоговый рост, часто ведёт к низкой самооценке и поведенческим проблемам. Слайды 24 и 28, заметки.</t>
+          <t>При преимущественно гипоталамическом поражении ТТГ бывает слегка повышен, как при субклиническом первичном гипотиреозе, но молекула лишена полной биологической активности, а св. Т4 уже низкий. Подтверждает механизм из 13.2a по вторичному источнику. Слайд 13, заметки.</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Persani L et al., Endocrine, 2021;71(3):681–688</t>
+          <t>Persani L et al. Endocr Connect 2019;8(2):R44–R54</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>33512657</t>
+          <t>30645189</t>
         </is>
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>10.1007/s12020-021-02626-z</t>
+          <t>10.1530/EC-18-0515</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>Мнение экспертов Endo-ERN</t>
+          <t>Экспертный обзор</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -14307,138 +14990,138 @@
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>"CDGP can be diagnosed only after exclusion of pathologically absent puberty… Leaving the diagnosis for later in life, though easier, may have negative consequences on adult height, and is frequently the cause of low self-esteem"</t>
+          <t>"TSH levels are superimposable to those generally found in subclinical or mild primary hypothyroidism, although the molecule is devoid of full biological activity and the FT4 is already in the hypothyroid range"</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>доп_S4</t>
+          <t>доп_S2</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>S4.06</t>
+          <t>S2.10</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>Проба с агонистом ГнРГ в работе Binder: трипторелин 0,1 мг, ЛГ через 4 ч; ингибин В определяли иммуноферментным методом, ЛГ — хемилюминесцентным. Уточняет 28.3. Слайд 28, таблица (строка 2) и заметки.</t>
+          <t>Центральный гипотиреоз, открывшийся на СТГ или половых стероидах, относится к картине дефицита нескольких гормонов гипофиза (дополняет 14.1b). Слайд 14, строка-ссылка по решению.</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Binder G et al., Clin Endocrinol (Oxf), 2015;82(1):100–105</t>
+          <t>Persani L et al. Endocr Connect 2019;8(2):R44–R54</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>25207430</t>
+          <t>30645189</t>
         </is>
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
-          <t>10.1111/cen.12613</t>
+          <t>10.1530/EC-18-0515</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>Когорта с наблюдением каждые 6 мес, n = 97 (в анализе 61)</t>
+          <t>Экспертный обзор</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация</t>
+          <t>подтверждено: аннотация и полный текст</t>
         </is>
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>"We assessed the accuracy of the GnRH agonist test (triptorelin 0·1 mg)… Inhibin B concentrations were measured by ELISA, and LH concentrations were measured by CLIA."</t>
+          <t>"The clinical management of CeH is further complicated by the combination with multiple pituitary deficiencies, as the introduction of sex steroids or GH replacements may uncover latent forms of CeH or increase the thyroxine requirements."</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>доп_S4</t>
+          <t>доп_S2</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>S4.07</t>
+          <t>S2.11</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Состав когорты Coutant: 16 изолированный гипогонадотропный гипогонадизм, 15 врождённый гипогонадотропный гипогонадизм в составе дефицита нескольких гормонов гипофиза, 51 конституциональная задержка; 1-я генитальная стадия (яички &lt; 3 мл): 9, 7 и 23; ранняя 2-я (3–6 мл): 7, 8 и 28. Уточняет 28.2. Слайд 28, заметки.</t>
+          <t>В консенсусе по врождённому гипотиреозу отдельной стартовой дозы для св. Т4 от 5 до 10 пмоль/л нет: названы тяжёлая форма (&lt; 5 пмоль/л, 10–15), лёгкая (&gt; 10 пмоль/л, около 10) и норма до лечения (возможно 5–10) при общем потолке 15 мкг/кг/сут (уточняет 15.1). Слайд 15, заметки.</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Coutant R et al., J Clin Endocrinol Metab, 2010;95(12):5225–5232</t>
+          <t>van Trotsenburg P et al. Thyroid 2021;31(3):387–419</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>20826577</t>
+          <t>33272083</t>
         </is>
       </c>
       <c r="F276" s="2" t="inlineStr">
         <is>
-          <t>10.1210/jc.2010-1535</t>
+          <t>10.1089/thy.2020.0333</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>Когорта с подтверждением диагноза наблюдением, n = 82</t>
+          <t>Раздел 3.1; 1/++0</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация</t>
+          <t>подтверждено: полный текст (PMC8001676; промежуточной категории нет)</t>
         </is>
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>"16 had IHH, 15 congenital HH within CPHD, and 51 CDP… genital stage 1 (testis volume&lt;3 ml; 9 IHH, 7 CPHD, and 23 CDP) or early stage 2 (testis volume, 3-6 ml; 7 IHH, 8 CPHD, and 28 CDP)"</t>
+          <t>"Infants with mild CH (fT4 &gt; 10 pmol/L in combination with elevated TSH) should be treated with the lowest initial dose (∼10 μg/kg per day)"</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>доп_S4</t>
+          <t>доп_S2</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>S4.08</t>
+          <t>S2.12</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Медиана возраста постановки диагноза синдрома Тернера — 15 лет, что задерживает консультирование и лечение; распространённость около 50 на 100 000 (1 на 2000). Слайд 30, заметки.</t>
+          <t>Национальное обследование Узбекистана: адекватно йодированная соль (&gt; 15 ppm) только в 36 % из 3413 домохозяйств; медиана йода в моче у небеременных некормящих женщин 140,9 мкг/л — йода достаточно; у беременных и кормящих — пограничная обеспеченность. Данные о женщинах, не о детях. Слайд 8, заметки.</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Gravholt CH et al., Lancet Diabetes Endocrinol, 2026 (онлайн; том и страницы в PubMed не указаны)</t>
+          <t>Rohner F, Nizamov F, Petry N, et al. Thyroid 2020;30(6):898–907</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>42790437</t>
+          <t>32098586</t>
         </is>
       </c>
       <c r="F277" s="2" t="inlineStr">
         <is>
-          <t>10.1016/S2213-8587(26)00192-0</t>
+          <t>10.1089/thy.2019.0788</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>Обзор</t>
+          <t>Поперечное популяционное обследование, 3413 домохозяйств</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
@@ -14448,185 +15131,185 @@
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>"Median age at diagnosis is 15 years, delaying appropriate counselling and treatment in many cases."</t>
+          <t>"Overall, 36% of 3413 households had adequately iodized salt" … "The median urinary iodine concentration (UIC) of 140.9 μg/L … in nonpregnant nonlactating women indicated adequate iodine status"</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>доп_S4</t>
+          <t>доп_S2</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>S4.09</t>
+          <t>S2.13</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>В подгруппах метаанализа андрогенов при конституциональной задержке тестостерон превзошёл оксандролон: +2,64 см (95 % ДИ 1,44–3,80); короткие курсы лучше длинных: +2,70 см (95 % ДИ 1,30–4,09). Данные ретроспективные. Уточняет 32.1c. Слайд 32, заметки.</t>
+          <t>Исправление к 12.1: дизайн Cerbone 2011 — поперечное (cross-sectional) контролируемое исследование, а не «перекрёстное»; детей до включения наблюдали в среднем 3,3 года. Слайд 12. В файле A строку 12.1 поправить при сведении.</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Wang L et al., BMC Endocr Disord, 2026;26(1)</t>
+          <t>Cerbone M et al. Eur J Endocrinol 2011;164(4):591–7</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>41933328</t>
+          <t>21292920</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
-          <t>10.1186/s12902-026-02253-7</t>
+          <t>10.1530/EJE-10-0979</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Метаанализ 13 ретроспективных когорт, n = 803; сравнение подгрупп</t>
+          <t>Поперечное контролируемое исследование, n = 36 + 36 контролей</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация</t>
+          <t>исправлено: аннотация</t>
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>"Short-course therapy was associated with greater improvement in final adult height compared with long-course therapy [MD = 2.70 cm…]. In addition, testosterone demonstrated superior efficacy compared with oxandrolone [MD = 2.64 cm, 95% CI (1.44, 3.80), P &lt; 0.001]."</t>
+          <t>"The aim of this cross-sectional, controlled study was to evaluate growth and intellectual outcome in children with persistent SH who have never been treated with levothyroxine."</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>доп_S4</t>
+          <t>доп_S3</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>S4.10</t>
+          <t>S3.01</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Форм эстрогенов для подростков нет, детские эндокринологи используют препараты для взрослых женщин вне инструкции; трансдермальный пластырь можно делить и так дробить дозу. Уточняет 32.3a и доп.2. Слайд 32, заметки.</t>
+          <t>Консенсус Общества гипофиза, раздел о детях: отсутствие прибавки роста при прибавке массы — самое частое проявление синдрома Кушинга у детей; поэтому у детей болезнь заметить несколько проще, чем у подростков после пубертата и у взрослых. Слайд 16, заметки.</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Nordenström A et al., Eur J Endocrinol, 2022;186(6):G9–G49</t>
+          <t>Fleseriu M, Auchus R, Bancos I et al. Lancet Diabetes Endocrinol 2021;9(12):847–875</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>35353710</t>
+          <t>34687601</t>
         </is>
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
-          <t>10.1530/EJE-22-0073</t>
+          <t>10.1016/S2213-8587(21)00235-7</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>Текст обоснования руководства Endo-ERN, без GRADE</t>
+          <t>Консенсус экспертов (Pituitary Society); раздел о детях без градации</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст</t>
+          <t>подтверждено: полный текст (PMC8743006)</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>"paediatricians have to deal with oestrogen formulations aimed for use by adult women (off-label). The possibility to split a transdermal patch, and thereby split the dose, facilitates mimicking the spontaneous increase in concentration"</t>
+          <t>"Lack of height gain concomitant with weight gain is the most common CS presentation in children, making the disorder somewhat easier to detect compared with post-pubertal adolescents or adults."</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>доп_S4</t>
+          <t>доп_S3</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>S4.11</t>
+          <t>S3.02</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Повторная проверка доп.1 раздела C: после индукции гонадотропинами сперматозоиды найдены у 18 из 25 обследованных (72 %); анализ эякулята делали после индукции, в возрасте 19 лет и старше. На слайд и в заметки не вошло (хронометраж), см. notes_for_editor слайда 33.</t>
+          <t>То же по обзору протокола NIH: самый частый первый симптом — прибавка массы; у детей самое частое проявление — рост, не прибавляющий вместе с массой. Слайд 16, заметки (поддержка S3.01).</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Yoo JE et al., Horm Res Paediatr, 2025;1–11 (онлайн)</t>
+          <t>Stratakis CA. Endocrinol Metab Clin North Am 2012;41(4):793–803</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>41442431</t>
+          <t>23099271</t>
         </is>
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t>10.1159/000550258</t>
+          <t>10.1016/j.ecl.2012.08.002</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>Ретроспективная когорта, n = 70</t>
+          <t>Нарративный обзор</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация</t>
+          <t>подтверждено: полный текст (PMC3594781)</t>
         </is>
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>"Sperm were detected in 72.0% (18/25) of the patients in the gonadotropin group… Semen analyses in both groups were performed only after completing pubertal induction and patients reached ≥19 years of age."</t>
+          <t>"The most common presenting symptom is weight gain; in childhood, lack of height gain consistent with the weight gain is the most common presentation of Cushing syndrome."</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>доп_S5</t>
+          <t>доп_S3</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>S5.01</t>
+          <t>S3.03</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>Уточнение 35.1a. Числа 80–200 и около 500 мкг/л — средние, а не референсный интервал: у детей до пубертата средние росли от 80 до 200 мкг/л, в пубертате круто поднимались примерно до 500. Метод — радиоиммунный анализ сыворотки после экстракции кислым этанолом. Слайд 35, заметки.</t>
+          <t>Японская ретроспективная серия: 19 детей с болезнью Кушинга (≤ 18 лет; 1994–2025, один центр; медиана возраста при диагнозе 13 лет, 6–17; 12 девочек). Рост в СО в среднем −0,45 в начале симптомов и −2,0 к диагнозу; ИМТ в СО +0,61 и +1,6. Прибавка массы со снижением скорости роста у 88,9 %. Медиана срока до диагноза 2,7 года (0,25–5,8). Слайд 16, заметки.</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Juul A et al. J Clin Endocrinol Metab 1994;78(3):744–752</t>
+          <t>Yamamoto M, Mukoyama Y, Kishi K et al. Endocr J 2026 (онлайн 02.07.2026; том и страницы в записи PubMed не указаны)</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>8126152</t>
+          <t>42386546</t>
         </is>
       </c>
       <c r="F281" s="2" t="inlineStr">
         <is>
-          <t>10.1210/jcem.78.3.8126152</t>
+          <t>10.1507/endocrj.EJ26-0212</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>Поперечное исследование, n = 1030 здоровых, Дания</t>
+          <t>Ретроспективная серия, один центр, n = 19</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -14636,898 +15319,2214 @@
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>"We measured IGF-I in acid-ethanol-extracted serum ... employing a RIA ... Mean serum IGF-I concentrations increased slowly in prepubertal children from 80-200 micrograms/L with a further steep increase during puberty to approximately 500 micrograms/L."</t>
+          <t>"The mean standard deviation scores (SDS) (SD) of height and body mass index (BMI) at onset and diagnosis were -0.45 (0.63) and -2.0 (1.1), and 0.61 (0.95) and 1.6 (0.75)" … "Median time to diagnosis was 2.7 (0.25-5.8) years."</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>доп_S5</t>
+          <t>доп_S3</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>S5.02</t>
+          <t>S3.04</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Уточнение 36.2. Попарное согласие шести методов по категориям СО авторы оценивают как умеренное или хорошее (взвешенная каппа 0,38–0,70); оценки «плохое» в аннотации нет. Интервалы на одной и той же здоровой выборке заметно различаются. Слайд 36, строка 5 и заметки.</t>
+          <t>Совет «ингаляционный глюкокортикоид ради роста не отменять, подбирать минимальную эффективную дозу» в аннотации кокрейновского обзора отсутствует. Аннотация говорит только, что торможение роста максимально в первый год и слабее в последующие. На слайд не ставится; в заметках слайда 18 — мнение лектора без ссылки на данные (решение по слайду 18).</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Chanson P et al. J Clin Endocrinol Metab 2016;101(9):3450–3458</t>
+          <t>Zhang L, Prietsch SO, Ducharme FM. Cochrane Database Syst Rev 2014;(7):CD009471</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>27167056</t>
+          <t>25030198</t>
         </is>
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>10.1210/jc.2016-1257</t>
+          <t>10.1002/14651858.CD009471.pub2</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Поперечное многоцентровое исследование, n = 911 здоровых взрослых, 6 иммуноанализов</t>
+          <t>Кокрейновский систематический обзор, 25 РКИ</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация</t>
+          <t>не подтверждено (в аннотации нет; полный текст не в списке доступных)</t>
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>"Pairwise concordances were moderate to good (0.38-0.70). ... Despite being obtained in the same healthy population, the reference intervals of the six commercial IGF-1 assay kits showed noteworthy differences. Agreement between methods was moderate to good."</t>
+          <t>Аннотация, вывод: "ICS-induced growth suppression seems to be maximal during the first year of therapy and less pronounced in subsequent years of treatment." О дозе как мере защиты роста не сказано.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>доп_S5</t>
+          <t>доп_S3</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>S5.03</t>
+          <t>S3.05</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>Молекулярная масса ИФР-1 человека 7649 (70 аминокислот, три дисульфидных мостика). Отсюда расчёт: 1 нг/мл = 1 мкг/л = 1000/7649 ≈ 0,131 нмоль/л; нмоль/л × 7,65 = нг/мл. Коэффициент — расчёт, опубликованного коэффициента для наборов не найдено (см. 37.1). Слайд 37, строка 5 и заметки.</t>
+          <t>Риск надпочечниковой недостаточности при отмене системных глюкокортикоидов после длительного приёма. В обоих полных текстах отмена экзогенных глюкокортикоидов не обсуждается: надпочечниковая недостаточность описана только после операции, при медикаментозном лечении и после адреналэктомии. На слайд 17 не ставится; в заметках — совет лектора (решение по слайду 17).</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Rinderknecht E, Humbel RE. J Biol Chem 1978;253(8):2769–2776</t>
+          <t>Stratakis CA. Endocrinol Metab Clin North Am 2012;41(4):793–803; Fleseriu M et al. Lancet Diabetes Endocrinol 2021;9(12):847–875</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>632300</t>
+          <t>23099271; 34687601</t>
         </is>
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
-          <t>— (в ответе инструмента DOI нет)</t>
+          <t>10.1016/j.ecl.2012.08.002; 10.1016/S2213-8587(21)00235-7</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Биохимическое исследование: аминокислотная последовательность</t>
+          <t>Нарративный обзор; консенсус экспертов</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация (масса); коэффициент — расчёт</t>
+          <t>не подтверждено (в полных текстах нет)</t>
         </is>
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>"IGF-I is a single chain polypeptide of 70 amino acid residues cross-linked by three disulfide bridges. The calculated molecular weight is 7649."</t>
+          <t>Нет цитаты: поиск по "withdraw", "taper", "exogenous", "adrenal insufficiency" в обоих полных текстах; об экзогенных глюкокортикоидах у Stratakis только "chronic administration of glucocorticoids or ACTH" как причина.</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>доп_S5</t>
+          <t>доп_S3</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>S5.04</t>
+          <t>S3.06</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Если СО считают после нормализации распределения (Бокс — Кокс, параметры асимметрии, медианы и вариации), границы 2,5-го и 97,5-го центиля соответствуют −1,96 и +1,96 СО, а 3-й центиль — −1,88 СО (квантили стандартного нормального распределения: 0,025 → −1,960; 0,03 → −1,881). Нормы Chanson даны как 2,5–97,5-й центили; у Wit нижняя граница — 3-й центиль. Слайд 37, строка 2 и заметки.</t>
+          <t>Опухоль коры надпочечника у малышей, выделяющая андрогены, при которой рост может не замедляться. В полном тексте Stratakis 2012 связи опухоли коры с андрогенами и сохранённым ростом нет; о вирилизации сказано только в общем перечне симптомов у детей в пубертате. На слайд 19 не ставится (решение по слайду 19).</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Chanson P et al. J Clin Endocrinol Metab 2016;101(9):3450–3458; расчёт</t>
+          <t>Stratakis CA. Endocrinol Metab Clin North Am 2012;41(4):793–803</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>27167056</t>
+          <t>23099271</t>
         </is>
       </c>
       <c r="F284" s="2" t="inlineStr">
         <is>
-          <t>10.1210/jc.2016-1257</t>
+          <t>10.1016/j.ecl.2012.08.002</t>
         </is>
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>Поперечное исследование, n = 911 взрослых (принцип); расчёт</t>
+          <t>Нарративный обзор</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация и расчёт</t>
+          <t>не подтверждено (в полном тексте нет)</t>
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>"Normative data included the range of values (2.5-97.5 percentiles) given by the six IGF-I assays according to age group and sex. A formula for SDS calculation is provided."</t>
+          <t>Единственное упоминание: "Pubertal children may present with virilization." Об андрогенах опухолей коры и росте при них не сказано.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>доп_S5</t>
+          <t>доп_S3</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>S5.05</t>
+          <t>S3.07</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>Пять категорий клинической вероятности дефицита СТГ до анализа определены через признаки «за» и «против»: высокая (около 50 % и выше) — несколько «за», ни одного «против»; умеренная (около 20 %) — часть «за», «против» нет; скорее низкая (около 10 %) — мало «за», «против» нет; низкая (около 5 %) — мало «за» и хотя бы одно «против»; очень низкая (около 2 % и меньше) — «за» нет и/или есть «против». Слайд 38, столбец 2 таблицы.</t>
+          <t>Полуночный кортизол сыворотки (&gt; 4,4 мкг/дл) в протоколе NIH берут после подтверждённого повышения суточного кортизола мочи (3 сбора); для точности суточный профиль требует госпитализации, что ограничивает его как рутинный скрининг. Слайд 20, таблица («в стационаре, после повышенного кортизола мочи») и заметки.</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+          <t>Stratakis CA. Endocrinol Metab Clin North Am 2012;41(4):793–803</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>31842524</t>
+          <t>23099271</t>
         </is>
       </c>
       <c r="F285" s="2" t="inlineStr">
         <is>
-          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+          <t>10.1016/j.ecl.2012.08.002</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Критический обзор; авторское предложение, мнение экспертов</t>
+          <t>Нарративный обзор (протокол NIH)</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст (PMC7291410)</t>
+          <t>подтверждено: полный текст</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>"High pre-test likelihood (≥≈50%), if there are several positive clues and no negative clues. ... Low pre-test likelihood (≈5%), if there are few positive clues and at least one negative clue for GHD."</t>
+          <t>"following confirmation of elevated 24-hour UFC (3 collections), a single midnight cortisol value of greater than 4.4 μg/dL" … "However, for accuracy, diurnal testing requires an inpatient stay, and this may limit its use as a routine screening test."</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>доп_S5</t>
+          <t>доп_S3</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>S5.06</t>
+          <t>S3.08</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Вес отдельных клинических признаков при оценке вероятности — личное мнение авторов обзора; наблюдательных данных нет, оценка субъективна. Список признаков дан в таблице статьи, в тексте PMC его нет. Слайд 38, заметки.</t>
+          <t>Малая двухдневная проба с дексаметазоном (30 мкг/кг на приём, не больше 0,5 мг, каждые 6 ч, 8 доз) в протоколе NIH — первая часть классической пробы Лиддла, которую проводят для поиска причины: при неподавлении в большой ночной пробе, отрицательной визуализации или подозрении на поражение надпочечников; оценивают кортизол мочи и 17-гидроксикортикостероиды. Слайд 20, заметки («тест центра для поиска причины»).</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+          <t>Stratakis CA. Endocrinol Metab Clin North Am 2012;41(4):793–803</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>31842524</t>
+          <t>23099271</t>
         </is>
       </c>
       <c r="F286" s="2" t="inlineStr">
         <is>
-          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+          <t>10.1016/j.ecl.2012.08.002</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>Критический обзор; мнение экспертов</t>
+          <t>Нарративный обзор (протокол NIH)</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст (PMC7291410)</t>
+          <t>подтверждено: полный текст</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>"shows the diagnostic clues and our personal opinion on their relative importance. Future prospective studies are needed to collect observational data on the relative weight of the various diagnostic clues."</t>
+          <t>"Indications for obtaining the classic Liddle's test, low-dose dexamethasone (30 μg/kg/dose; maximum 0.5 mg/dose) every 6 hours for 8 doses … include nonsuppression of serum cortisol levels during the HDDST and/or negative imaging studies, and/or suspected adrenal disease."</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>доп_S5</t>
+          <t>доп_S3</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>S5.07</t>
+          <t>S3.09</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>Умеренная вероятность (около 20 %): при пороге 0 СО вероятность после анализа примерно равна исходной, при −1 СО — 30 %; авторы предлагают порог ИФР-1 ниже 0 СО. Заголовок категории в тексте PMC утерян; принадлежность абзаца умеренной категории следует из порядка абзацев и арифметики: отношение правдоподобия, дающее 10 → 16 % при −1 СО, из 20 % даёт ровно 30 %. Высокая категория: проба при любом ИФР-1 (вероятность после анализа при ИФР-1 ниже 0 СО &gt; 52–70 %). Слайд 38, таблица.</t>
+          <t>Суточную мочу у детей амбулаторно часто трудно собрать надёжно. Ложно высокий свободный кортизол мочи: в том числе при тяжёлом хроническом ожирении и большом объёме выпитой жидкости; ложно низкий — в основном при неполном сборе. Уточняет 21.1b (ожирение «тяжёлое хроническое», «высокий водный режим» теперь подтверждён полным текстом). Слайд 21, таблица и заметки.</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+          <t>Stratakis CA. Endocrinol Metab Clin North Am 2012;41(4):793–803</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>31842524</t>
+          <t>23099271</t>
         </is>
       </c>
       <c r="F287" s="2" t="inlineStr">
         <is>
-          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+          <t>10.1016/j.ecl.2012.08.002</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>Критический обзор; расчёт авторов на голландской когорте детей от 4 лет</t>
+          <t>Нарративный обзор</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст и расчёт</t>
+          <t>подтверждено: полный текст</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>"At a cut-off of 0 SDS the post-test likelihood is approximately equal to the pre-test likelihood, and at a cut-off of -1 SDS it is 30%. We suggest that in such cases a serum IGF-I &lt;0 SDS can be used"</t>
+          <t>"it is often difficult to obtain a 24-hour urine collection reliably in the outpatient setting, particularly in the pediatric population" … "chronic and severe obesity … and high water intake" … "falsely low UFC may be obtained mostly with inadequate collection."</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>доп_S5</t>
+          <t>доп_S3</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>S5.08</t>
+          <t>S3.10</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Низкая вероятность (около 5 %): вероятность после анализа выше 10 % только при пороге −2 СО; очень низкая (около 2 % и меньше): ниже 10 % при любом ИФР-1. Скорее низкая (около 10 %): порог −1 СО (с 10 до 16 %, см. 38.1). Слайд 38, таблица.</t>
+          <t>Подтверждённая прибавка роста — простой способ отличить ребёнка с псевдо-Кушингом от ребёнка с синдромом Кушинга. Слайд 21, заметки.</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+          <t>Stratakis CA. Endocrinol Metab Clin North Am 2012;41(4):793–803</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>31842524</t>
+          <t>23099271</t>
         </is>
       </c>
       <c r="F288" s="2" t="inlineStr">
         <is>
-          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+          <t>10.1016/j.ecl.2012.08.002</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>Критический обзор; расчёт авторов</t>
+          <t>Нарративный обзор (мнение автора)</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст (PMC7291410)</t>
+          <t>подтверждено: полный текст</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>"At a low pre-test likelihood the post-test likelihood is only above 10% at a cut-off point of -2.0 SDS, while at a very low likelihood the post-test likelihood remains below 10% at all values of the IGF-I results."</t>
+          <t>"Confirmed height gain is a simple way to help distinguish children with pseudo-Cushing from those with Cushing syndrome."</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>доп_S5</t>
+          <t>доп_S3</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>S5.09</t>
+          <t>S3.11</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>Уточнение 38.1. При низкой и очень низкой вероятности первый шаг — повтор ИФР-1 вместе с ИФРСБ-3; дальше обследуют, если повторный ИФР-1 снова низкий, а ИФРСБ-3 низкий или низконормальный. Слайд 38, строки «Низкая» и «Очень низкая», заметки.</t>
+          <t>У 5–10 % больных секреция кортизола периодическая, и ночная проба с 1 мг дексаметазона и суточный кортизол мочи могут быть нормальными; при подозрении на периодический синдром Кушинга советуют продолжать наблюдение, включая рост и суточный кортизол мочи. Слайд 21, заметки.</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+          <t>Stratakis CA. Endocrinol Metab Clin North Am 2012;41(4):793–803</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>31842524</t>
+          <t>23099271</t>
         </is>
       </c>
       <c r="F289" s="2" t="inlineStr">
         <is>
-          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+          <t>10.1016/j.ecl.2012.08.002</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>Критический обзор; авторское предложение</t>
+          <t>Нарративный обзор</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст (PMC7291410)</t>
+          <t>подтверждено: полный текст</t>
         </is>
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>"... at (very) low pre-test likelihood ... repeat an IGF-I determination, in combination with serum IGFBP-3. If this IGF-I result is in line with the first one and is supported by a low or low-normal IGFBP-3 SDS, further investigations are warranted"</t>
+          <t>"5% to 10% of patients may have intermittent or periodic cortisol hypersecretion and may not manifest abnormal results to either test. If periodic or intermittent Cushing syndrome is suspected, continuous follow-up … including monitoring of growth and 24-hour UFC."</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>доп_S5</t>
+          <t>доп_S3</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>S5.10</t>
+          <t>S3.12</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Числовой поправки ИФР-1 на ИМТ и питание нет: наблюдательных данных не хватает, остаётся клиническое суждение врача (поправка на стадию пубертата, в отличие от питания, возможна). Слайд 38, строка 1.</t>
+          <t>Ночная проба с дексаметазоном может быть ненадёжной у женщин, принимающих эстрогены внутрь (рекомендация для взрослых). Слайд 21, заметки (вывод лектора: девушке на эстрогенах начинать с мочи или слюны).</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+          <t>Fleseriu M et al. Lancet Diabetes Endocrinol 2021;9(12):847–875</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>31842524</t>
+          <t>34687601</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
-          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+          <t>10.1016/S2213-8587(21)00235-7</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>Критический обзор; мнение экспертов</t>
+          <t>Консенсус экспертов; HQ, SR (высокое качество, сильная)</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст (PMC7291410)</t>
+          <t>подтверждено: полный текст</t>
         </is>
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>"Due to the lack of observational data, a formal adjustment of the IGF-I result for BMI is not possible, so that the clinician can only use his/her subjective clinical judgement."</t>
+          <t>"DST may be the preferred test for shift workers and patients with disrupted circadian rhythm due to uneven sleep schedules, but may not be reliable in women treated with oral estrogen (HQ, SR)."</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>доп_S5</t>
+          <t>доп_S3</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>S5.11</t>
+          <t>S3.13</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>Порог −2 СО, который предлагает большинство работ, пропускает около 35 % детей с дефицитом СТГ. Слайд 38, заметки («около трети»).</t>
+          <t>Раздел о детях: после успешного лечения функция надпочечников обычно восстанавливается примерно за 12 мес. Слайд 23, тело.</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+          <t>Fleseriu M et al. Lancet Diabetes Endocrinol 2021;9(12):847–875</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>31842524</t>
+          <t>34687601</t>
         </is>
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+          <t>10.1016/S2213-8587(21)00235-7</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>Критический обзор; расчёт по чувствительности 65 % голландской когорты</t>
+          <t>Консенсус экспертов; раздел о детях без градации</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст (PMC7291410)</t>
+          <t>подтверждено: полный текст</t>
         </is>
       </c>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>"Most papers suggest that IGF-I should be below -2 SDS, but it is obvious that this would imply that approximately 35% of children with GHD would not be detected."</t>
+          <t>"With successful treatment, adrenal function typically recovers within approximately 12 months."</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>доп_S5</t>
+          <t>доп_S3</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>S5.12</t>
+          <t>S3.14</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Уточнение 40.1a: у допубертатных детей с ожирением ИФРСБ-3 при диагнозе достоверно повышен и возвращается к норме после снижения ИМТ. Слайд 40, таблица (ячейка без пометки «сверить»).</t>
+          <t>Больным в ремиссии после операции нужна заместительная терапия глюкокортикоидами до восстановления оси гипоталамус — гипофиз — надпочечники (общий раздел, без градации). Слайд 23, тело.</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>Argente J et al. J Clin Endocrinol Metab 1997;82(7):2076–2083</t>
+          <t>Fleseriu M et al. Lancet Diabetes Endocrinol 2021;9(12):847–875</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>9215275</t>
+          <t>34687601</t>
         </is>
       </c>
       <c r="F292" s="2" t="inlineStr">
         <is>
-          <t>10.1210/jcem.82.7.4089</t>
+          <t>10.1016/S2213-8587(21)00235-7</t>
         </is>
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>Сравнительное исследование: 65 допубертатных детей с ожирением и контроли</t>
+          <t>Консенсус экспертов; раздел «Background», без градации</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация</t>
+          <t>подтверждено: полный текст</t>
         </is>
       </c>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>"Serum IGFBP-3 and GHBP levels were increased significantly at diagnosis and returned to normal levels after a reduction in the BMI SD score."</t>
+          <t>"Patients in remission require GC replacement until HPA axis recovery."</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>доп_S5</t>
+          <t>доп_S3</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>S5.13</t>
+          <t>S3.15</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>У детей с избыточной массой оптимальный порог ИФР-1 для направления на пробу, по предположению авторов обзора, может быть выше, чем при нормальном ИМТ. Слайд 40, заметки.</t>
+          <t>После успешной операции при болезни Кушинга или удаления аденомы надпочечника наступает период надпочечниковой недостаточности до восстановления оси; сразу после операции — стрессовые дозы с быстрым снижением до физиологической (12–15 мг/м² в сутки в 2–3 приёма); стрессовые дозы при острой болезни, травме и операции нужны и при временной, и при постоянной недостаточности. Слайд 23, тело и заметки.</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+          <t>Stratakis CA. Endocrinol Metab Clin North Am 2012;41(4):793–803</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>31842524</t>
+          <t>23099271</t>
         </is>
       </c>
       <c r="F293" s="2" t="inlineStr">
         <is>
-          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+          <t>10.1016/j.ecl.2012.08.002</t>
         </is>
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>Критический обзор; мнение экспертов (предположение)</t>
+          <t>Нарративный обзор</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст (PMC7291410)</t>
+          <t>подтверждено: полный текст</t>
         </is>
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>"In overweight children, one could therefore expect that the optimal cut-off point of IGF-I for the decision to perform a GH stimulation test may be higher than in children with a normal BMI SDS."</t>
+          <t>"After the completion of successful TSS in Cushing disease … there will be a period of adrenal insufficiency while the hypothalamic pituitary adrenal axis is recovering." … "stress dosing for acute illness, trauma, or surgical procedures is required for both temporary and permanent adrenal insufficiency."</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>доп_S5</t>
+          <t>доп_S3</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>S5.14</t>
+          <t>S3.16</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Уточнение 40.2. 14 больных болезнью Кушинга и 14 контролей того же пола и стадии пубертата; СТГ каждые 20 мин 24 ч до и через 10–11 дней, 3, 6 и 12 мес после аденомэктомии. Подавление СТГ сохранялось не меньше года при нормальном ИФР-1, хотя у 4 растущих больных (стадия Таннера III и ниже) рост ускорился. В выборке подростки и взрослые. Слайд 40, заметки.</t>
+          <t>Пожизненное наблюдение за рецидивом болезни Кушинга (рекомендация для взрослых). Слайд 23, тело.</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>Magiakou MA et al. J Clin Endocrinol Metab 1994;78(1):131–137</t>
+          <t>Fleseriu M et al. Lancet Diabetes Endocrinol 2021;9(12):847–875</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>7507118</t>
+          <t>34687601</t>
         </is>
       </c>
       <c r="F294" s="2" t="inlineStr">
         <is>
-          <t>10.1210/jcem.78.1.7507118</t>
+          <t>10.1016/S2213-8587(21)00235-7</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>Клиническое исследование, n = 14 и 14 контролей; наблюдение 12 мес</t>
+          <t>Консенсус экспертов; MQ, SR (умеренное качество, сильная)</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация</t>
+          <t>подтверждено: полный текст</t>
         </is>
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>"In these patients, plasma IGF-I and GHBP remained normal ... GH hyposecretion continues for at least a year during convalescence, in spite of significant increases in the growth rate in all growing patients."</t>
+          <t>"We recommend lifelong monitoring for recurrence of CD (MQ, SR)."</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>доп_S5</t>
+          <t>доп_S3</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>S5.15</t>
+          <t>S3.17</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>Уточнение 40.5c. Две семьи, 8 больных, возраст при диагнозе 13–24 года: у всех высокий базальный СТГ, а дальше высокий ИФР-1 и/или неподавляемый СТГ при пероральной нагрузке глюкозой. Слайд 40, строка «Избыток СТГ».</t>
+          <t>После лучевой терапии пожизненно наблюдают и за дефицитом гормонов гипофиза, и за рецидивом (рекомендация для взрослых). Слайд 23, тело.</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>Gadelha MR et al. J Clin Endocrinol Metab 1999;84(1):249–256</t>
+          <t>Fleseriu M et al. Lancet Diabetes Endocrinol 2021;9(12):847–875</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>9920092</t>
+          <t>34687601</t>
         </is>
       </c>
       <c r="F295" s="2" t="inlineStr">
         <is>
-          <t>10.1210/jcem.84.1.5370</t>
+          <t>10.1016/S2213-8587(21)00235-7</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>Серия случаев, n = 8 (2 семьи)</t>
+          <t>Консенсус экспертов; HQ, SR (высокое качество, сильная)</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация</t>
+          <t>подтверждено: полный текст</t>
         </is>
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>"All 8 affected patients had elevated basal GH levels associated with high insulin-like growth factor I levels and/or nonsuppressible serum GH levels during an oral glucose tolerance test."</t>
+          <t>"Lifelong monitoring for pituitary hormone deficiencies and recurrence is required in all patients undergoing RT (HQ, SR)."</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>доп_S5</t>
+          <t>доп_S3</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>S5.16</t>
+          <t>S3.18</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Уточнение 41.3a. Повтор ИФР-1 стоит рассмотреть прежде всего при расхождении клиники и результата; при наблюдении одного пациента используют один и тот же метод. Слайд 41, строка 1.</t>
+          <t>Частота рецидива после успешной операции в публикациях 5–35 %; половина рецидивов в первые 5 лет, половина позже, вплоть до 10 лет и более (данные о взрослых). Слайд 23, заметки.</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+          <t>Fleseriu M et al. Lancet Diabetes Endocrinol 2021;9(12):847–875</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>31842524</t>
+          <t>34687601</t>
         </is>
       </c>
       <c r="F296" s="2" t="inlineStr">
         <is>
-          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+          <t>10.1016/S2213-8587(21)00235-7</t>
         </is>
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>Критический обзор; мнение экспертов</t>
+          <t>Консенсус экспертов; обзор литературы («Background»)</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст (PMC7291410)</t>
+          <t>подтверждено: полный текст</t>
         </is>
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>"repetition of an IGF-I determination should be considered, particularly if there is a discrepancy between the clinical features and the laboratory results. Given the inter-assay variation, it is advisable to use the same assay during follow-up"</t>
+          <t>"Published recurrence rates vary between 5% and 35%, with half appearing within the first 5 years after surgery and half after up to 10 years or more."</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>доп_S5</t>
+          <t>доп_S3</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>S5.17</t>
+          <t>S3.19</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>Внутриметодная вариация ИФР-1: коэффициент вариации 6–8 % в методе Тюбингена и общий коэффициент вариации 3,4–8,7 % у iSYS; это довод за повтор. Слайд 41, заметки («почти до 9 %»).</t>
+          <t>Общество гипофиза советует начинать с ночной пробы с дексаметазоном, суточного свободного кортизола мочи и/или кортизола слюны поздно вечером в зависимости от местной доступности; несколько проб слюны пациенту выполнить проще. Это проверенная часть цитаты из 20.1b (строка 20.1b в файле B помечена «не подтверждено» как утверждение об утреннем кортизоле). Слайд 20, тело, строка 1.</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+          <t>Fleseriu M et al. Lancet Diabetes Endocrinol 2021;9(12):847–875</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>31842524</t>
+          <t>34687601</t>
         </is>
       </c>
       <c r="F297" s="2" t="inlineStr">
         <is>
-          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+          <t>10.1016/S2213-8587(21)00235-7</t>
         </is>
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>Критический обзор (цитирование характеристик методов)</t>
+          <t>Консенсус экспертов; HQ, SR (высокое качество, сильная)</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст (PMC7291410)</t>
+          <t>подтверждено: полный текст</t>
         </is>
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>"For each assay there is also some intra-assay variation [e.g., a coefficient of variation of 6-8% in the assay used in Tübingen () and a total coefficient of variation 3.4-8.7% in the iSYS assay ()]"</t>
+          <t>"We recommend starting with DST, UFC, and/or LNSC (HQ, SR) depending on local availability; multiple LNSCs may be easier for the patient to complete (HQ, SR)."</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>доп_S5</t>
+          <t>доп_S4</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>S5.18</t>
+          <t>S4.01</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>У ребёнка с низким ИМТ, другими признаками недоедания или после болезни со сниженным аппетитом низкий ИФР-1 малоинформативен; по возможности сначала улучшают питание, потом повторяют ИФР-1. Слайд 41, строка 2.</t>
+          <t>Авторы метаанализа о сдвиге телархе призывают пересмотреть определение преждевременного пубертата: традиционное определение может устареть. О пересмотре порогов задержки пубертата в аннотации не сказано. Слайд 25, заметки.</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+          <t>Eckert-Lind C et al., JAMA Pediatr, 2020;174(4):e195881</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>31842524</t>
+          <t>32040143</t>
         </is>
       </c>
       <c r="F298" s="2" t="inlineStr">
         <is>
-          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+          <t>10.1001/jamapediatrics.2019.5881</t>
         </is>
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>Критический обзор; мнение экспертов</t>
+          <t>Систематический обзор и метаанализ, 30 исследований</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: полный текст (PMC7291410)</t>
+          <t>подтверждено: аннотация</t>
         </is>
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>"This would imply that in such children a low serum IGF-I has a relatively low predictive value. If feasible, one may wish to first improve the nutritional condition before repeating further IGF-I measurements."</t>
+          <t>"The medical community needs current and relevant data to redefine "precocious puberty," because the traditional definition may be outdated, at least in some regions of the world."</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>доп_S5</t>
+          <t>доп_S4</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>S5.19</t>
+          <t>S4.02</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>Руководство ESPGHAN 2020: антитела к деамидированным пептидам глиадина (IgG и IgA) для первичного обследования на целиакию не рекомендуются; тест на IgG — только при низком или неопределяемом общем IgA. Слайд 41, заметки. Сила рекомендации в аннотации не указана, формулировка «We recommend against».</t>
+          <t>Изолированное лобковое и подмышечное оволосение зависит в основном от андрогенов надпочечников и не означает начала гонадотропин-зависимого пубертата; первый признак пубертата у мальчиков — увеличение яичек (объём больше 3 мл). Слайд 25, заметки.</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>Husby S et al. J Pediatr Gastroenterol Nutr 2020;70(1):141–156 (ESPGHAN; не ESPE)</t>
+          <t>Persani L et al., Endocrine, 2021;71(3):681–688</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>31568151</t>
+          <t>33512657</t>
         </is>
       </c>
       <c r="F299" s="2" t="inlineStr">
         <is>
-          <t>10.1097/MPG.0000000000002497</t>
+          <t>10.1007/s12020-021-02626-z</t>
         </is>
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>Руководство, GRADE и QUADAS-2</t>
+          <t>Мнение экспертов Endo-ERN (обзор, не руководство)</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>подтверждено: аннотация</t>
+          <t>подтверждено: полный текст</t>
         </is>
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>"We recommend against deamidated gliadin peptide antibodies (DGP-IgG/IgA) for initial testing. Only if total IgA is low/undetectable, an IgG-based test is indicated."</t>
+          <t>"The appearance of pubic and axillary hair is mainly dependent upon adrenal androgens and, if isolated, should not be interpreted as the beginning of gonadotrophin-dependent puberty"</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
+          <t>доп_S4</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>S4.03</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>Если к 13 (девочки) или 14 (мальчики) годам признаков пубертата нет, первым шагом определяют гонадотропины и костный возраст; высокие гонадотропины указывают на первичный дефект гонад, и ключевой шаг — кариотип. Слайд 26, заметки.</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>Persani L et al., Endocrine, 2021;71(3):681–688</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>33512657</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>10.1007/s12020-021-02626-z</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>Мнение экспертов Endo-ERN (предложенный алгоритм)</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: полный текст</t>
+        </is>
+      </c>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>"the determination of gonadotropins and bone age can be useful as a first diagnostic approach. High gonadotropins point to a primary gonadal defect and karyotype is a key step for the definition of these cases."</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>доп_S4</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>S4.04</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>Мальчика с недоразвитым (на 2,5 СО и больше ниже среднего), но в остальном нормальным половым членом без гипоспадии обследуют на врождённый гипогонадотропный гипогонадизм: базальные гормоны оси в минипубертат (около 1–4 мес после рождения), позже — проба с ХГЧ. Слайд 27, заметки.</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>Persani L et al., Endocrine, 2021;71(3):681–688</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>33512657</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>10.1007/s12020-021-02626-z</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>Мнение экспертов Endo-ERN</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: полный текст</t>
+        </is>
+      </c>
+      <c r="I301" s="2" t="inlineStr">
+        <is>
+          <t>"should be further investigated to exclude CHH, based on baseline assessment of the HPG axis during minipuberty (~1–4 months after birth), or an HCG stimulation test thereafter"</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>доп_S4</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>S4.05</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>Конституциональную задержку диагностируют только после исключения гипергонадотропного и врождённого гипогонадотропного гипогонадизма. Откладывать диагноз на поздний возраст не следует: это может снизить итоговый рост, часто ведёт к низкой самооценке и поведенческим проблемам. Слайды 24 и 28, заметки.</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>Persani L et al., Endocrine, 2021;71(3):681–688</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>33512657</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>10.1007/s12020-021-02626-z</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>Мнение экспертов Endo-ERN</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: полный текст</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>"CDGP can be diagnosed only after exclusion of pathologically absent puberty… Leaving the diagnosis for later in life, though easier, may have negative consequences on adult height, and is frequently the cause of low self-esteem"</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>доп_S4</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>S4.06</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>Проба с агонистом ГнРГ в работе Binder: трипторелин 0,1 мг, ЛГ через 4 ч; ингибин В определяли иммуноферментным методом, ЛГ — хемилюминесцентным. Уточняет 28.3. Слайд 28, таблица (строка 2) и заметки.</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>Binder G et al., Clin Endocrinol (Oxf), 2015;82(1):100–105</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>25207430</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>10.1111/cen.12613</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>Когорта с наблюдением каждые 6 мес, n = 97 (в анализе 61)</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: аннотация</t>
+        </is>
+      </c>
+      <c r="I303" s="2" t="inlineStr">
+        <is>
+          <t>"We assessed the accuracy of the GnRH agonist test (triptorelin 0·1 mg)… Inhibin B concentrations were measured by ELISA, and LH concentrations were measured by CLIA."</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>доп_S4</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>S4.07</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>Состав когорты Coutant: 16 изолированный гипогонадотропный гипогонадизм, 15 врождённый гипогонадотропный гипогонадизм в составе дефицита нескольких гормонов гипофиза, 51 конституциональная задержка; 1-я генитальная стадия (яички &lt; 3 мл): 9, 7 и 23; ранняя 2-я (3–6 мл): 7, 8 и 28. Уточняет 28.2. Слайд 28, заметки.</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>Coutant R et al., J Clin Endocrinol Metab, 2010;95(12):5225–5232</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>20826577</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>10.1210/jc.2010-1535</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>Когорта с подтверждением диагноза наблюдением, n = 82</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: аннотация</t>
+        </is>
+      </c>
+      <c r="I304" s="2" t="inlineStr">
+        <is>
+          <t>"16 had IHH, 15 congenital HH within CPHD, and 51 CDP… genital stage 1 (testis volume&lt;3 ml; 9 IHH, 7 CPHD, and 23 CDP) or early stage 2 (testis volume, 3-6 ml; 7 IHH, 8 CPHD, and 28 CDP)"</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>доп_S4</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>S4.08</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>Медиана возраста постановки диагноза синдрома Тернера — 15 лет, что задерживает консультирование и лечение; распространённость около 50 на 100 000 (1 на 2000). Слайд 30, заметки.</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>Gravholt CH et al., Lancet Diabetes Endocrinol, 2026 (онлайн; том и страницы в PubMed не указаны)</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>42790437</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/S2213-8587(26)00192-0</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>Обзор</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: аннотация</t>
+        </is>
+      </c>
+      <c r="I305" s="2" t="inlineStr">
+        <is>
+          <t>"Median age at diagnosis is 15 years, delaying appropriate counselling and treatment in many cases."</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>доп_S4</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>S4.09</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>В подгруппах метаанализа андрогенов при конституциональной задержке тестостерон превзошёл оксандролон: +2,64 см (95 % ДИ 1,44–3,80); короткие курсы лучше длинных: +2,70 см (95 % ДИ 1,30–4,09). Данные ретроспективные. Уточняет 32.1c. Слайд 32, заметки.</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>Wang L et al., BMC Endocr Disord, 2026;26(1)</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>41933328</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>10.1186/s12902-026-02253-7</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>Метаанализ 13 ретроспективных когорт, n = 803; сравнение подгрупп</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: аннотация</t>
+        </is>
+      </c>
+      <c r="I306" s="2" t="inlineStr">
+        <is>
+          <t>"Short-course therapy was associated with greater improvement in final adult height compared with long-course therapy [MD = 2.70 cm…]. In addition, testosterone demonstrated superior efficacy compared with oxandrolone [MD = 2.64 cm, 95% CI (1.44, 3.80), P &lt; 0.001]."</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>доп_S4</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>S4.10</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>Форм эстрогенов для подростков нет, детские эндокринологи используют препараты для взрослых женщин вне инструкции; трансдермальный пластырь можно делить и так дробить дозу. Уточняет 32.3a и доп.2. Слайд 32, заметки.</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>Nordenström A et al., Eur J Endocrinol, 2022;186(6):G9–G49</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>35353710</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>10.1530/EJE-22-0073</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>Текст обоснования руководства Endo-ERN, без GRADE</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: полный текст</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>"paediatricians have to deal with oestrogen formulations aimed for use by adult women (off-label). The possibility to split a transdermal patch, and thereby split the dose, facilitates mimicking the spontaneous increase in concentration"</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>доп_S4</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>S4.11</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>Повторная проверка доп.1 раздела C: после индукции гонадотропинами сперматозоиды найдены у 18 из 25 обследованных (72 %); анализ эякулята делали после индукции, в возрасте 19 лет и старше. На слайд и в заметки не вошло (хронометраж), см. notes_for_editor слайда 33.</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>Yoo JE et al., Horm Res Paediatr, 2025;1–11 (онлайн)</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>41442431</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>10.1159/000550258</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>Ретроспективная когорта, n = 70</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: аннотация</t>
+        </is>
+      </c>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>"Sperm were detected in 72.0% (18/25) of the patients in the gonadotropin group… Semen analyses in both groups were performed only after completing pubertal induction and patients reached ≥19 years of age."</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
           <t>доп_S5</t>
         </is>
       </c>
-      <c r="B300" s="2" t="inlineStr">
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>S5.01</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>Уточнение 35.1a. Числа 80–200 и около 500 мкг/л — средние, а не референсный интервал: у детей до пубертата средние росли от 80 до 200 мкг/л, в пубертате круто поднимались примерно до 500. Метод — радиоиммунный анализ сыворотки после экстракции кислым этанолом. Слайд 35, заметки.</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>Juul A et al. J Clin Endocrinol Metab 1994;78(3):744–752</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>8126152</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>10.1210/jcem.78.3.8126152</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>Поперечное исследование, n = 1030 здоровых, Дания</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: аннотация</t>
+        </is>
+      </c>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>"We measured IGF-I in acid-ethanol-extracted serum ... employing a RIA ... Mean serum IGF-I concentrations increased slowly in prepubertal children from 80-200 micrograms/L with a further steep increase during puberty to approximately 500 micrograms/L."</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>доп_S5</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>S5.02</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>Уточнение 36.2. Попарное согласие шести методов по категориям СО авторы оценивают как умеренное или хорошее (взвешенная каппа 0,38–0,70); оценки «плохое» в аннотации нет. Интервалы на одной и той же здоровой выборке заметно различаются. Слайд 36, строка 5 и заметки.</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>Chanson P et al. J Clin Endocrinol Metab 2016;101(9):3450–3458</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>27167056</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>10.1210/jc.2016-1257</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>Поперечное многоцентровое исследование, n = 911 здоровых взрослых, 6 иммуноанализов</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: аннотация</t>
+        </is>
+      </c>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>"Pairwise concordances were moderate to good (0.38-0.70). ... Despite being obtained in the same healthy population, the reference intervals of the six commercial IGF-1 assay kits showed noteworthy differences. Agreement between methods was moderate to good."</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>доп_S5</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>S5.03</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>Молекулярная масса ИФР-1 человека 7649 (70 аминокислот, три дисульфидных мостика). Отсюда расчёт: 1 нг/мл = 1 мкг/л = 1000/7649 ≈ 0,131 нмоль/л; нмоль/л × 7,65 = нг/мл. Коэффициент — расчёт, опубликованного коэффициента для наборов не найдено (см. 37.1). Слайд 37, строка 5 и заметки.</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>Rinderknecht E, Humbel RE. J Biol Chem 1978;253(8):2769–2776</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>632300</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>— (в ответе инструмента DOI нет)</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>Биохимическое исследование: аминокислотная последовательность</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: аннотация (масса); коэффициент — расчёт</t>
+        </is>
+      </c>
+      <c r="I311" s="2" t="inlineStr">
+        <is>
+          <t>"IGF-I is a single chain polypeptide of 70 amino acid residues cross-linked by three disulfide bridges. The calculated molecular weight is 7649."</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>доп_S5</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>S5.04</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>Если СО считают после нормализации распределения (Бокс — Кокс, параметры асимметрии, медианы и вариации), границы 2,5-го и 97,5-го центиля соответствуют −1,96 и +1,96 СО, а 3-й центиль — −1,88 СО (квантили стандартного нормального распределения: 0,025 → −1,960; 0,03 → −1,881). Нормы Chanson даны как 2,5–97,5-й центили; у Wit нижняя граница — 3-й центиль. Слайд 37, строка 2 и заметки.</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>Chanson P et al. J Clin Endocrinol Metab 2016;101(9):3450–3458; расчёт</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>27167056</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>10.1210/jc.2016-1257</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>Поперечное исследование, n = 911 взрослых (принцип); расчёт</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: аннотация и расчёт</t>
+        </is>
+      </c>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>"Normative data included the range of values (2.5-97.5 percentiles) given by the six IGF-I assays according to age group and sex. A formula for SDS calculation is provided."</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>доп_S5</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>S5.05</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>Пять категорий клинической вероятности дефицита СТГ до анализа определены через признаки «за» и «против»: высокая (около 50 % и выше) — несколько «за», ни одного «против»; умеренная (около 20 %) — часть «за», «против» нет; скорее низкая (около 10 %) — мало «за», «против» нет; низкая (около 5 %) — мало «за» и хотя бы одно «против»; очень низкая (около 2 % и меньше) — «за» нет и/или есть «против». Слайд 38, столбец 2 таблицы.</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>31842524</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>Критический обзор; авторское предложение, мнение экспертов</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: полный текст (PMC7291410)</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>"High pre-test likelihood (≥≈50%), if there are several positive clues and no negative clues. ... Low pre-test likelihood (≈5%), if there are few positive clues and at least one negative clue for GHD."</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>доп_S5</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>S5.06</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>Вес отдельных клинических признаков при оценке вероятности — личное мнение авторов обзора; наблюдательных данных нет, оценка субъективна. Список признаков дан в таблице статьи, в тексте PMC его нет. Слайд 38, заметки.</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>31842524</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>Критический обзор; мнение экспертов</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: полный текст (PMC7291410)</t>
+        </is>
+      </c>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>"shows the diagnostic clues and our personal opinion on their relative importance. Future prospective studies are needed to collect observational data on the relative weight of the various diagnostic clues."</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>доп_S5</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>S5.07</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>Умеренная вероятность (около 20 %): при пороге 0 СО вероятность после анализа примерно равна исходной, при −1 СО — 30 %; авторы предлагают порог ИФР-1 ниже 0 СО. Заголовок категории в тексте PMC утерян; принадлежность абзаца умеренной категории следует из порядка абзацев и арифметики: отношение правдоподобия, дающее 10 → 16 % при −1 СО, из 20 % даёт ровно 30 %. Высокая категория: проба при любом ИФР-1 (вероятность после анализа при ИФР-1 ниже 0 СО &gt; 52–70 %). Слайд 38, таблица.</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>31842524</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>Критический обзор; расчёт авторов на голландской когорте детей от 4 лет</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: полный текст и расчёт</t>
+        </is>
+      </c>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>"At a cut-off of 0 SDS the post-test likelihood is approximately equal to the pre-test likelihood, and at a cut-off of -1 SDS it is 30%. We suggest that in such cases a serum IGF-I &lt;0 SDS can be used"</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>доп_S5</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>S5.08</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>Низкая вероятность (около 5 %): вероятность после анализа выше 10 % только при пороге −2 СО; очень низкая (около 2 % и меньше): ниже 10 % при любом ИФР-1. Скорее низкая (около 10 %): порог −1 СО (с 10 до 16 %, см. 38.1). Слайд 38, таблица.</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>31842524</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>Критический обзор; расчёт авторов</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: полный текст (PMC7291410)</t>
+        </is>
+      </c>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>"At a low pre-test likelihood the post-test likelihood is only above 10% at a cut-off point of -2.0 SDS, while at a very low likelihood the post-test likelihood remains below 10% at all values of the IGF-I results."</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>доп_S5</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>S5.09</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>Уточнение 38.1. При низкой и очень низкой вероятности первый шаг — повтор ИФР-1 вместе с ИФРСБ-3; дальше обследуют, если повторный ИФР-1 снова низкий, а ИФРСБ-3 низкий или низконормальный. Слайд 38, строки «Низкая» и «Очень низкая», заметки.</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>31842524</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>Критический обзор; авторское предложение</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: полный текст (PMC7291410)</t>
+        </is>
+      </c>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>"... at (very) low pre-test likelihood ... repeat an IGF-I determination, in combination with serum IGFBP-3. If this IGF-I result is in line with the first one and is supported by a low or low-normal IGFBP-3 SDS, further investigations are warranted"</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>доп_S5</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>S5.10</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>Числовой поправки ИФР-1 на ИМТ и питание нет: наблюдательных данных не хватает, остаётся клиническое суждение врача (поправка на стадию пубертата, в отличие от питания, возможна). Слайд 38, строка 1.</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>31842524</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>Критический обзор; мнение экспертов</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: полный текст (PMC7291410)</t>
+        </is>
+      </c>
+      <c r="I318" s="2" t="inlineStr">
+        <is>
+          <t>"Due to the lack of observational data, a formal adjustment of the IGF-I result for BMI is not possible, so that the clinician can only use his/her subjective clinical judgement."</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>доп_S5</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>S5.11</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>Порог −2 СО, который предлагает большинство работ, пропускает около 35 % детей с дефицитом СТГ. Слайд 38, заметки («около трети»).</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>31842524</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>Критический обзор; расчёт по чувствительности 65 % голландской когорты</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: полный текст (PMC7291410)</t>
+        </is>
+      </c>
+      <c r="I319" s="2" t="inlineStr">
+        <is>
+          <t>"Most papers suggest that IGF-I should be below -2 SDS, but it is obvious that this would imply that approximately 35% of children with GHD would not be detected."</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>доп_S5</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>S5.12</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>Уточнение 40.1a: у допубертатных детей с ожирением ИФРСБ-3 при диагнозе достоверно повышен и возвращается к норме после снижения ИМТ. Слайд 40, таблица (ячейка без пометки «сверить»).</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>Argente J et al. J Clin Endocrinol Metab 1997;82(7):2076–2083</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>9215275</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>10.1210/jcem.82.7.4089</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>Сравнительное исследование: 65 допубертатных детей с ожирением и контроли</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: аннотация</t>
+        </is>
+      </c>
+      <c r="I320" s="2" t="inlineStr">
+        <is>
+          <t>"Serum IGFBP-3 and GHBP levels were increased significantly at diagnosis and returned to normal levels after a reduction in the BMI SD score."</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>доп_S5</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>S5.13</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>У детей с избыточной массой оптимальный порог ИФР-1 для направления на пробу, по предположению авторов обзора, может быть выше, чем при нормальном ИМТ. Слайд 40, заметки.</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>31842524</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="inlineStr">
+        <is>
+          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+        </is>
+      </c>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>Критический обзор; мнение экспертов (предположение)</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: полный текст (PMC7291410)</t>
+        </is>
+      </c>
+      <c r="I321" s="2" t="inlineStr">
+        <is>
+          <t>"In overweight children, one could therefore expect that the optimal cut-off point of IGF-I for the decision to perform a GH stimulation test may be higher than in children with a normal BMI SDS."</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>доп_S5</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>S5.14</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>Уточнение 40.2. 14 больных болезнью Кушинга и 14 контролей того же пола и стадии пубертата; СТГ каждые 20 мин 24 ч до и через 10–11 дней, 3, 6 и 12 мес после аденомэктомии. Подавление СТГ сохранялось не меньше года при нормальном ИФР-1, хотя у 4 растущих больных (стадия Таннера III и ниже) рост ускорился. В выборке подростки и взрослые. Слайд 40, заметки.</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>Magiakou MA et al. J Clin Endocrinol Metab 1994;78(1):131–137</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>7507118</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>10.1210/jcem.78.1.7507118</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>Клиническое исследование, n = 14 и 14 контролей; наблюдение 12 мес</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: аннотация</t>
+        </is>
+      </c>
+      <c r="I322" s="2" t="inlineStr">
+        <is>
+          <t>"In these patients, plasma IGF-I and GHBP remained normal ... GH hyposecretion continues for at least a year during convalescence, in spite of significant increases in the growth rate in all growing patients."</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>доп_S5</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>S5.15</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>Уточнение 40.5c. Две семьи, 8 больных, возраст при диагнозе 13–24 года: у всех высокий базальный СТГ, а дальше высокий ИФР-1 и/или неподавляемый СТГ при пероральной нагрузке глюкозой. Слайд 40, строка «Избыток СТГ».</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>Gadelha MR et al. J Clin Endocrinol Metab 1999;84(1):249–256</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>9920092</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>10.1210/jcem.84.1.5370</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>Серия случаев, n = 8 (2 семьи)</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: аннотация</t>
+        </is>
+      </c>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>"All 8 affected patients had elevated basal GH levels associated with high insulin-like growth factor I levels and/or nonsuppressible serum GH levels during an oral glucose tolerance test."</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>доп_S5</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>S5.16</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>Уточнение 41.3a. Повтор ИФР-1 стоит рассмотреть прежде всего при расхождении клиники и результата; при наблюдении одного пациента используют один и тот же метод. Слайд 41, строка 1.</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>31842524</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>Критический обзор; мнение экспертов</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: полный текст (PMC7291410)</t>
+        </is>
+      </c>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>"repetition of an IGF-I determination should be considered, particularly if there is a discrepancy between the clinical features and the laboratory results. Given the inter-assay variation, it is advisable to use the same assay during follow-up"</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>доп_S5</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>S5.17</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>Внутриметодная вариация ИФР-1: коэффициент вариации 6–8 % в методе Тюбингена и общий коэффициент вариации 3,4–8,7 % у iSYS; это довод за повтор. Слайд 41, заметки («почти до 9 %»).</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>31842524</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
+          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+        </is>
+      </c>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>Критический обзор (цитирование характеристик методов)</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: полный текст (PMC7291410)</t>
+        </is>
+      </c>
+      <c r="I325" s="2" t="inlineStr">
+        <is>
+          <t>"For each assay there is also some intra-assay variation [e.g., a coefficient of variation of 6-8% in the assay used in Tübingen () and a total coefficient of variation 3.4-8.7% in the iSYS assay ()]"</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>доп_S5</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>S5.18</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>У ребёнка с низким ИМТ, другими признаками недоедания или после болезни со сниженным аппетитом низкий ИФР-1 малоинформативен; по возможности сначала улучшают питание, потом повторяют ИФР-1. Слайд 41, строка 2.</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12(2):130–139</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>31842524</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>10.4274/jcrpe.galenos.2019.2019.0176</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>Критический обзор; мнение экспертов</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: полный текст (PMC7291410)</t>
+        </is>
+      </c>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>"This would imply that in such children a low serum IGF-I has a relatively low predictive value. If feasible, one may wish to first improve the nutritional condition before repeating further IGF-I measurements."</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>доп_S5</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>S5.19</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>Руководство ESPGHAN 2020: антитела к деамидированным пептидам глиадина (IgG и IgA) для первичного обследования на целиакию не рекомендуются; тест на IgG — только при низком или неопределяемом общем IgA. Слайд 41, заметки. Сила рекомендации в аннотации не указана, формулировка «We recommend against».</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>Husby S et al. J Pediatr Gastroenterol Nutr 2020;70(1):141–156 (ESPGHAN; не ESPE)</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>31568151</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>10.1097/MPG.0000000000002497</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>Руководство, GRADE и QUADAS-2</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>подтверждено: аннотация</t>
+        </is>
+      </c>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>"We recommend against deamidated gliadin peptide antibodies (DGP-IgG/IgA) for initial testing. Only if total IgA is low/undetectable, an IgG-based test is indicated."</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>доп_S5</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
         <is>
           <t>S5.20</t>
         </is>
       </c>
-      <c r="C300" s="2" t="inlineStr">
+      <c r="C328" s="2" t="inlineStr">
         <is>
           <t>Поперечное ретроспективное исследование: 1242 ребёнка 2–9 лет до пубертата с ростом ниже −1 СО; ИМТ в СО и ИФР-1 в СО связаны линейно и положительно; отношение св. Т3 к св. Т4 объясняет 9,12 % связи. Связь статистическая, авторы просят проспективной проверки. Не использовано (заметки слайда 41 на пределе хронометража).</t>
         </is>
       </c>
-      <c r="D300" s="2" t="inlineStr">
+      <c r="D328" s="2" t="inlineStr">
         <is>
           <t>Zhang M, Liu H. Front Endocrinol (Lausanne) 2026;17:1941425</t>
         </is>
       </c>
-      <c r="E300" s="2" t="inlineStr">
+      <c r="E328" s="2" t="inlineStr">
         <is>
           <t>42824137</t>
         </is>
       </c>
-      <c r="F300" s="2" t="inlineStr">
+      <c r="F328" s="2" t="inlineStr">
         <is>
           <t>10.3389/fendo.2026.1941425</t>
         </is>
       </c>
-      <c r="G300" s="2" t="inlineStr">
+      <c r="G328" s="2" t="inlineStr">
         <is>
           <t>Поперечное ретроспективное исследование, n = 1242, Китай</t>
         </is>
       </c>
-      <c r="H300" s="2" t="inlineStr">
+      <c r="H328" s="2" t="inlineStr">
         <is>
           <t>подтверждено: аннотация; не использовано</t>
         </is>
       </c>
-      <c r="I300" s="2" t="inlineStr">
+      <c r="I328" s="2" t="inlineStr">
         <is>
           <t>"In this growth-retarded prepubertal cohort, BMI and IGF-1 are linearly associated. The FT3/FT4 ratio is statistically supported as a partial mediator with moderate effect size"</t>
         </is>
@@ -15544,7 +17543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -15570,7 +17569,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -15580,7 +17579,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -15590,7 +17589,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -15600,7 +17599,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -15610,257 +17609,337 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Догоняющий рост</t>
+          <t>зона роста</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Дозы левотироксина</t>
+          <t>старение зоны роста</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Центральный гипотиреоз, св. Т4 как критерий</t>
+          <t>догоняющий рост: механизм</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Системные глюкокортикоиды и рост</t>
+          <t>гипотиреоз: механизм задержки роста</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Местные глюкокортикоиды и рост</t>
+          <t>Догоняющий рост</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Тесты на гиперкортицизм</t>
+          <t>Дозы левотироксина</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Направление в центр при гиперкортицизме</t>
+          <t>Центральный гипотиреоз, св. Т4 как критерий</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Дефицит СТГ после лечения Кушинга</t>
+          <t>глюкокортикоиды: механизм задержки роста</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Конституциональная задержка роста и пубертата</t>
+          <t>Системные глюкокортикоиды и рост</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Стадии Таннера, объём яичек</t>
+          <t>Местные глюкокортикоиды и рост</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Пороги задержки пубертата</t>
+          <t>Тесты на гиперкортицизм</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Функциональный гипогонадотропный гипогонадизм</t>
+          <t>Направление в центр при гиперкортицизме</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Врождённый гипогонадотропный гипогонадизм: клиника</t>
+          <t>Дефицит СТГ после лечения Кушинга</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Врождённый гипогонадотропный гипогонадизм: анализы</t>
+          <t>Конституциональная задержка роста и пубертата</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Евнухоидные пропорции</t>
+          <t>Стадии Таннера, объём яичек</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Кариотип при низкорослости у девочки</t>
+          <t>Пороги задержки пубертата</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>СТГ при синдроме Тернера</t>
+          <t>Функциональный гипогонадотропный гипогонадизм</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Дозы и темп индукции пубертата</t>
+          <t>Врождённый гипогонадотропный гипогонадизм: клиника</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Переход во взрослую сеть</t>
+          <t>Врождённый гипогонадотропный гипогонадизм: анализы</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ИФР-1: что отражает</t>
+          <t>эстрогены: пубертатный скачок и закрытие зон роста</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ИФРСБ-3</t>
+          <t>Кариотип при низкорослости у девочки</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ИФР-1 в СО по полу и пубертату</t>
+          <t>ген SHOX</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Анализаторы и стандартизация</t>
+          <t>синдром Тернера: механизм низкорослости</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Единицы и пересчёт</t>
+          <t>СТГ при синдроме Тернера</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>Дозы и темп индукции пубертата</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Переход во взрослую сеть</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>ИФР-1: что отражает</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>ИФРСБ-3</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>ИФР-1 в СО по полу и пубертату</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Анализаторы и стандартизация</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Единицы и пересчёт</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
           <t>Претестовая вероятность и порог</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n">
-        <v>38</v>
+      <c r="B38" s="2" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>ось СТГ — ИФР-1: где ломается при других болезнях</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -15932,13 +18011,21 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Раскрытие конфликта интересов: [текст автора]</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
+          <t>Первым делом смотрите, что отстаёт раньше: рост или масса</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>правило сравнения: рабочий приём докладчика, данных нет; целиакия: вводная часть систематического обзора</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Mameli C et al. Ital J Pediatr 2026;52(1), PMID 41723458</t>
+        </is>
+      </c>
       <c r="E3" s="2" t="n">
-        <v>83</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4">
@@ -15947,13 +18034,21 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>После лекции вы отличите четыре эндокринные причины низкорослости по кривой и анализам</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
+          <t>Одно измерение роста мало что говорит, решает скорость роста</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>систематический обзор, 42 исследования</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Mameli C et al. Ital J Pediatr 2026;52(1), PMID 41723458 (описание метода Таннера: среднее роста родителей ±6,5 см); Tanner JM et al. Arch Dis Child 1970;45:755–62 (центильные таблицы с поправкой на рост родителей)</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="n">
-        <v>87</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5">
@@ -15962,21 +18057,21 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>По четырём разделам рекомендации выпустили разные общества в 2015–2025 годах</t>
+          <t>Костный возраст показывает запас роста, но причину не называет</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>руководства, консенсусы экспертов и Дельфи-опрос</t>
+          <t>когорта, n = 24, разность средних; мнение экспертов Европейской референсной сети; нарративный обзор</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>van Trotsenburg 2021, Thyroid; Persani 2018, Eur Thyroid J; Fleseriu 2021, Lancet Diabetes Endocrinol; Tabarin 2022 и Martinerie 2024, Ann Endocrinol; Korbonits 2024, Nat Rev Endocrinol; Nordenström 2022 и Gravholt 2024, Eur J Endocrinol; Boehm 2015, Nat Rev Endocrinol; Grimberg 2016, Horm Res Paediatr; Arlien-Søborg 2025, Pituitary; поиск по PubMed, 2022–2026</t>
+          <t>Rivkees SA et al. N Engl J Med 1988;318:599–602; Persani L et al. Endocrine 2021;71:681–8; Martin DD et al. Horm Res Paediatr 2011;76:1–9</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6">
@@ -15985,21 +18080,21 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Первым делом смотрите, что отстаёт раньше: рост или масса</t>
+          <t>Кость растёт в длину в зоне роста, и каждая болезнь действует на своё звено</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>правило сравнения: рабочий приём докладчика, данных нет; целиакия: вводная часть систематического обзора</t>
+          <t>обзоры; задержка старения зоны роста — опыты на кроликах и крысах, у людей данные косвенные</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Mameli C et al. Ital J Pediatr 2026;52(1), PMID 41723458</t>
+          <t>Baron J et al. Nat Rev Endocrinol 2015;11:735–46; Emons J et al. Horm Res Paediatr 2011;75:383–91; Lui JC et al. Endocr Dev 2011;21:23–9; Hochberg Z. Horm Res 2002;58 Suppl 1:33–8; Shao YY et al. Rev Endocr Metab Disord 2006;7:265–71; Weise M et al. Proc Natl Acad Sci USA 2001;98:6871–6</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -16008,21 +18103,21 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Одно измерение роста мало что говорит, решает скорость роста</t>
+          <t>При приобретённом гипотиреозе отставание в росте бывает первым признаком</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>систематический обзор, 42 исследования</t>
+          <t>нарративный обзор с 4 клиническими случаями</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Mameli C et al. Ital J Pediatr 2026;52(1), PMID 41723458 (описание метода Таннера: среднее роста родителей ±6,5 см); Tanner JM et al. Arch Dis Child 1970;45:755–62 (центильные таблицы с поправкой на рост родителей)</t>
+          <t>Salerno M et al. Front Endocrinol (Lausanne) 2026;16:1744280; Rohner F et al. Thyroid 2020;30:898–907</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8">
@@ -16031,21 +18126,21 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Костный возраст показывает запас роста, но причину не называет</t>
+          <t>Без гормона щитовидной железы хрящ плохо окостеневает, а секреция СТГ падает</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>когорта, n = 24, разность средних; мнение экспертов Европейской референсной сети; нарративный обзор</t>
+          <t>обзоры; исследование 7 детей до и на лечении; опыты на крысах</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Rivkees SA et al. N Engl J Med 1988;318:599–602; Persani L et al. Endocrine 2021;71:681–8; Martin DD et al. Horm Res Paediatr 2011;76:1–9</t>
+          <t>Williams GR, Bassett JHD. J Endocrinol Invest 2018;41:99–109; Chernausek SD, Turner R. J Pediatr 1989;114:968–72; Cavallo F et al. Front Pediatr 2021;9:580314; Marino R et al. Endocrinology 2008;149:1820–8</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -16054,21 +18149,21 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>При приобретённом гипотиреозе отставание в росте бывает первым признаком</t>
+          <t>Чем дольше гипотиреоз не выявлен, тем больше потеря итогового роста</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>нарративный обзор с 4 клиническими случаями</t>
+          <t>когорта, n = 24, тяжёлый первичный гипотиреоз</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Salerno M et al. Front Endocrinol (Lausanne) 2026;16:1744280; Rohner F et al. Thyroid 2020;30:898–907</t>
+          <t>Rivkees SA et al. N Engl J Med 1988;318:599–602</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>101</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -16077,21 +18172,21 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Чем дольше гипотиреоз не выявлен, тем больше потеря итогового роста</t>
+          <t>Догоняющий рост тем полнее, чем раньше начато лечение и чем дальше до пубертата</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>когорта, n = 24, тяжёлый первичный гипотиреоз</t>
+          <t>дозы и малый старт: мнение авторов нарративного обзора; серия случаев, n = 4</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Rivkees SA et al. N Engl J Med 1988;318:599–602</t>
+          <t>Salerno M et al. Front Endocrinol (Lausanne) 2026;16:1744280; Boersma B et al. Eur J Pediatr 1996;155:362–7</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11">
@@ -16100,21 +18195,21 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Догоняющий рост тем полнее, чем раньше начато лечение и чем дальше до пубертата</t>
+          <t>У ребёнка с давним гипотиреозом кость на лечении созревает быстрее, чем идёт рост</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>дозы и малый старт: мнение авторов нарративного обзора; серия случаев, n = 4</t>
+          <t>когорта, n = 24; ретроспективное сравнение, n = 33; описание случая, n = 1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Salerno M et al. Front Endocrinol (Lausanne) 2026;16:1744280; Boersma B et al. Eur J Pediatr 1996;155:362–7</t>
+          <t>Rivkees SA et al. N Engl J Med 1988;318:599–602; Teng L et al. J Pediatr Endocrinol Metab 2004;17:345–54; Salerno M et al. Front Endocrinol (Lausanne) 2026;16:1744280; Minamitani K et al. Arch Dis Child 1994;70:429–30</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -16123,21 +18218,21 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>У ребёнка с давним гипотиреозом кость на лечении созревает быстрее, чем идёт рост</t>
+          <t>Идиопатический субклинический гипотиреоз рост не замедляет, при отставании ищут другую причину</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>когорта, n = 24; ретроспективное сравнение, n = 33; описание случая, n = 1</t>
+          <t>поперечное, n = 36; когорты, n = 92 и 111; другая причина: мнение докладчика</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Rivkees SA et al. N Engl J Med 1988;318:599–602; Teng L et al. J Pediatr Endocrinol Metab 2004;17:345–54; Salerno M et al. Front Endocrinol (Lausanne) 2026;16:1744280; Minamitani K et al. Arch Dis Child 1994;70:429–30</t>
+          <t>Cerbone M et al. Eur J Endocrinol 2011;164:591–7; Wasniewska M et al. Eur J Endocrinol 2009;160:417–21; Zengin NŞ et al. J Clin Res Pediatr Endocrinol 2026;18:498–507</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>99</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13">
@@ -16146,21 +18241,21 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Идиопатический субклинический гипотиреоз рост не замедляет, при отставании ищут другую причину</t>
+          <t>При центральном гипотиреозе ТТГ бывает нормальным, диагноз ставят по св. Т4</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>поперечное, n = 36; когорты, n = 92 и 111; другая причина: мнение докладчика</t>
+          <t>экспертный обзор; Европейская референсная сеть (новорождённые): диагноз и цель сильные, по надпочечникам слабая</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Cerbone M et al. Eur J Endocrinol 2011;164:591–7; Wasniewska M et al. Eur J Endocrinol 2009;160:417–21; Zengin NŞ et al. J Clin Res Pediatr Endocrinol 2026;18:498–507</t>
+          <t>Persani L et al. Endocr Connect 2019;8:R44–R54; van Trotsenburg P et al. Thyroid 2021;31:387–419; Boelen A et al. Handb Clin Neurol 2021;180:161–169</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14">
@@ -16169,21 +18264,21 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>При центральном гипотиреозе ТТГ бывает нормальным, диагноз ставят по св. Т4</t>
+          <t>После начала лечения СТГ св. Т4 снижается, и части детей нужен левотироксин</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>экспертный обзор; Европейская референсная сеть (новорождённые): диагноз и цель сильные, по надпочечникам слабая</t>
+          <t>проспективное наблюдение, n = 15; когорта, n = 75; экспертный обзор</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Persani L et al. Endocr Connect 2019;8:R44–R54; van Trotsenburg P et al. Thyroid 2021;31:387–419; Boelen A et al. Handb Clin Neurol 2021;180:161–169</t>
+          <t>Wyatt DT et al. J Clin Endocrinol Metab 1998;83:3493–7; Smyczyńska J et al. Thyroid Res 2010;3:2; Persani L et al. Endocr Connect 2019;8:R44–R54</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -16192,21 +18287,21 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>После начала лечения СТГ св. Т4 снижается, и части детей нужен левотироксин</t>
+          <t>При раннем и достаточном лечении врождённого гипотиреоза итоговый рост не страдает</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>проспективное наблюдение, n = 15; когорта, n = 75; экспертный обзор</t>
+          <t>Европейская референсная сеть: сильные, качество умеренное и высокое; ретроспективная когорта, n = 172</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Wyatt DT et al. J Clin Endocrinol Metab 1998;83:3493–7; Smyczyńska J et al. Thyroid Res 2010;3:2; Persani L et al. Endocr Connect 2019;8:R44–R54</t>
+          <t>van Trotsenburg P et al. Thyroid 2021;31:387–419 (Endo-ERN, одобрено ESPE и ESE); Niuro L et al. Horm Res Paediatr 2023;96:376–84</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -16215,21 +18310,21 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>При раннем и достаточном лечении врождённого гипотиреоза итоговый рост не страдает</t>
+          <t>Ребёнок с ожирением выше сверстников, а ребёнок с гиперкортицизмом ниже</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Европейская референсная сеть: сильные, качество умеренное и высокое; ретроспективная когорта, n = 172</t>
+          <t>сравнение двух групп, n = 25 и 41; серии случаев, n = 59 и 19</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>van Trotsenburg P et al. Thyroid 2021;31:387–419 (Endo-ERN, одобрено ESPE и ESE); Niuro L et al. Horm Res Paediatr 2023;96:376–84</t>
+          <t>Greening JE et al. J Endocrinol Invest 2006;29:885–7; Magiakou MA et al. N Engl J Med 1994;331:629–36; Yamamoto M et al. Endocr J 2026, PMID 42386546; Fleseriu M et al. Lancet Diabetes Endocrinol 2021;9:847–75 (Pituitary Society)</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17">
@@ -16238,21 +18333,21 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Ребёнок с ожирением выше сверстников, а ребёнок с гиперкортицизмом ниже</t>
+          <t>Избыток глюкокортикоидов тормозит рост в гипофизе, в тканях и в самой зоне роста</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>сравнение двух групп, n = 25 и 41; серии случаев, n = 59 и 19</t>
+          <t>обзоры; опыты на кроликах</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Greening JE et al. J Endocrinol Invest 2006;29:885–7; Magiakou MA et al. N Engl J Med 1994;331:629–36; Yamamoto M et al. Endocr J 2026, PMID 42386546; Fleseriu M et al. Lancet Diabetes Endocrinol 2021;9:847–75 (Pituitary Society)</t>
+          <t>Mazziotti G, Giustina A. Nat Rev Endocrinol 2013;9:265–76; Hochberg Z. Horm Res 2002;58 Suppl 1:33–8; Stratakis CA. Endocrinol Metab Clin North Am 2012;41:793–803; Gafni RI et al. Pediatr Res 2001;50:618–23</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>111</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18">
@@ -16537,21 +18632,21 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Изолированный гипогонадизм даёт высокий рост, низкорослость с ним указывает на вторую причину</t>
+          <t>Без эстрогенов нет скачка и зоны роста долго открыты: при врождённом гипогонадизме рост высокий</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>мнение экспертов Европейской референсной сети; текст её руководства без оценки качества; вторая причина: мнение докладчика</t>
+          <t>обзоры; опыты на кроликах; описания случаев; мнение экспертов Европейской референсной сети</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Persani L et al. Endocrine 2021;71:681–8; Nordenström A et al. Eur J Endocrinol 2022;186:G9–G49</t>
+          <t>Grumbach MM. J Pediatr Endocrinol Metab 2000;13 Suppl 6:1439–55; Juul A. Hum Reprod Update 2001;7:303–13; Weise M et al. Proc Natl Acad Sci USA 2001;98:6871–6; Smith EP et al. N Engl J Med 1994;331:1056–61; Morishima A et al. J Clin Endocrinol Metab 1995;80:3689–98; Persani L et al. Endocrine 2021;71:681–8; Nordenström A et al. Eur J Endocrinol 2022;186:G9–G49</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31">
@@ -16583,21 +18678,21 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>При синдроме Тернера СТГ можно начинать с 2 лет, эстрогены вводят с 11–12 лет</t>
+          <t>При синдроме Тернера рост теряется прежде всего из-за нехватки гена *SHOX*</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Европейское общество эндокринологии и Общество детских эндокринологов (США): сильные рекомендации; прибавка роста — обзор исследований</t>
+          <t>руководство Европейского общества эндокринологии и Общества детских эндокринологов (США); обзор</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Gravholt CH et al. Eur J Endocrinol 2024;190:G53–G151</t>
+          <t>Gravholt CH et al. Eur J Endocrinol 2024;190:G53–G151; Marchini A et al. Endocr Rev 2016;37:417–48</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33">
@@ -16606,21 +18701,21 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Малые дозы при индукции явной потери роста не дали, но данных мало</t>
+          <t>При синдроме Тернера СТГ можно начинать с 2 лет, эстрогены вводят с 11–12 лет</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>метаанализы 6 и 2 исследований, 13 ретроспективных когорт; дозы: Европейская референсная сеть, руководство по Тернеру</t>
+          <t>Европейское общество эндокринологии и Общество детских эндокринологов (США): сильные рекомендации; прибавка роста — обзор исследований</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Nordenström A et al. Eur J Endocrinol 2022;186:G9–G49; Gravholt CH et al. Eur J Endocrinol 2024;190:G53–G151; Wang L et al. BMC Endocr Disord 2026;26(1), PMID 41933328; Gawlik-Starzyk A et al. Horm Res Paediatr 2025;98:327–35; Ross JL et al. N Engl J Med 2011;364:1230–42</t>
+          <t>Gravholt CH et al. Eur J Endocrinol 2024;190:G53–G151</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>115</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34">
@@ -16629,21 +18724,21 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>При гипогонадизме терапия после индукции постоянная, и пациента передают взрослому эндокринологу</t>
+          <t>Малые дозы при индукции явной потери роста не дали, но данных мало</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Европейская референсная сеть: рекомендация, предложение и текст обоснования; руководство по Тернеру: сильная рекомендация</t>
+          <t>метаанализы 6 и 2 исследований, 13 ретроспективных когорт; дозы: Европейская референсная сеть, руководство по Тернеру</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Nordenström A et al. Eur J Endocrinol 2022;186:G9–G49; Gravholt CH et al. Eur J Endocrinol 2024;190:G53–G151; Boehm U et al. Nat Rev Endocrinol 2015;11:547–64; Shihadeh F et al. Horm Res Paediatr 2026, PMID 42721063; Cianfarani S et al. Horm Res Paediatr 2026, PMID 41553972</t>
+          <t>Nordenström A et al. Eur J Endocrinol 2022;186:G9–G49; Gravholt CH et al. Eur J Endocrinol 2024;190:G53–G151; Wang L et al. BMC Endocr Disord 2026;26(1), PMID 41933328; Gawlik-Starzyk A et al. Horm Res Paediatr 2025;98:327–35; Ross JL et al. N Engl J Med 2011;364:1230–42</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35">
@@ -16652,21 +18747,21 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ИФРСБ-3 специфичнее ИФР-1, но пропускает половину случаев дефицита СТГ</t>
+          <t>При гипогонадизме терапия после индукции постоянная, и пациента передают взрослому эндокринологу</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>метаанализ, 12 исследований; поперечное, n = 131; практика Нидерландов по критическому обзору</t>
+          <t>Европейская референсная сеть: рекомендация, предложение и текст обоснования; руководство по Тернеру: сильная рекомендация</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Shen Y et al. Eur J Pediatr 2015;174:419–27; Cianfarani S et al. J Clin Endocrinol Metab 2005;90:6028–34; Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12:130–9</t>
+          <t>Nordenström A et al. Eur J Endocrinol 2022;186:G9–G49; Gravholt CH et al. Eur J Endocrinol 2024;190:G53–G151; Boehm U et al. Nat Rev Endocrinol 2015;11:547–64; Shihadeh F et al. Horm Res Paediatr 2026, PMID 42721063; Cianfarani S et al. Horm Res Paediatr 2026, PMID 41553972</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36">
@@ -16675,21 +18770,21 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ИФР-1 сравнивают с нормой по полу и стадии пубертата, при задержке учитывают костный возраст</t>
+          <t>ИФРСБ-3 специфичнее ИФР-1, но пропускает половину случаев дефицита СТГ</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>поперечное исследование, Турция, n = 807; критический обзор, мнение экспертов</t>
+          <t>метаанализ, 12 исследований; поперечное, n = 131; практика Нидерландов по критическому обзору</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Bereket A et al. Horm Res 2006;65:96–105; Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12:130–9; Juul A et al. J Clin Endocrinol Metab 1994;78:744–52</t>
+          <t>Shen Y et al. Eur J Pediatr 2015;174:419–27; Cianfarani S et al. J Clin Endocrinol Metab 2005;90:6028–34; Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12:130–9</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>114</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37">
@@ -16698,21 +18793,21 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Разные анализаторы дают разный ИФР-1, и норма годится только для своего метода</t>
+          <t>ИФР-1 сравнивают с нормой по полу и стадии пубертата, при задержке учитывают костный возраст</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>консенсус экспертов; характеристика стандарта, 18 лабораторий; поперечное, 6 методов, n = 911 взрослых</t>
+          <t>поперечное исследование, Турция, n = 807; критический обзор, мнение экспертов</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Clemmons DR. Clin Chem 2011;57:555–9; Burns C et al. Growth Horm IGF Res 2009;19:457–62; Chanson P et al. J Clin Endocrinol Metab 2016;101:3450–8</t>
+          <t>Bereket A et al. Horm Res 2006;65:96–105; Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12:130–9; Juul A et al. J Clin Endocrinol Metab 1994;78:744–52</t>
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38">
@@ -16721,21 +18816,21 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Если лаборатория дала только интервал, СО считают по нормам того же метода</t>
+          <t>Разные анализаторы дают разный ИФР-1, и норма годится только для своего метода</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>поперечное исследование, n = 911 взрослых (принцип расчёта); совет для детей: мнение докладчика</t>
+          <t>консенсус экспертов; характеристика стандарта, 18 лабораторий; поперечное, 6 методов, n = 911 взрослых</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Chanson P et al. J Clin Endocrinol Metab 2016;101:3450–8; Bidlingmaier M et al. J Clin Endocrinol Metab 2014;99:1712–21; Rinderknecht E, Humbel RE. J Biol Chem 1978;253:2769–76</t>
+          <t>Clemmons DR. Clin Chem 2011;57:555–9; Burns C et al. Growth Horm IGF Res 2009;19:457–62; Chanson P et al. J Clin Endocrinol Metab 2016;101:3450–8</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39">
@@ -16744,21 +18839,21 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Порог в СО для проб зависит от вероятности дефицита СТГ до анализа</t>
+          <t>Если лаборатория дала только интервал, СО считают по нормам того же метода</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>схема критического обзора, мнение экспертов; Дельфи-опрос: 18 детских и 25 взрослых эндокринологов</t>
+          <t>поперечное исследование, n = 911 взрослых (принцип расчёта); совет для детей: мнение докладчика</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12:130–9; Arlien-Søborg MC et al. Pituitary 2025;28:57 (GRS)</t>
+          <t>Chanson P et al. J Clin Endocrinol Metab 2016;101:3450–8; Bidlingmaier M et al. J Clin Endocrinol Metab 2014;99:1712–21; Rinderknecht E, Humbel RE. J Biol Chem 1978;253:2769–76</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40">
@@ -16767,21 +18862,21 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Низкий для возраста ИФР-1 дают гипотиреоз, задержка пубертата, голод и воспаление</t>
+          <t>Порог в СО для проб зависит от вероятности дефицита СТГ до анализа</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>когорта, n = 15; сравнения с контролем, n = 14–36; опыты на мышах; обзоры</t>
+          <t>схема критического обзора, мнение экспертов; Дельфи-опрос: 18 детских и 25 взрослых эндокринологов</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Zamboni G et al. Acta Paediatr 2000;89:1050–5; Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12:130–9; Bereket A et al. Horm Res 2006;65:96–105; Zamboni G et al. Pediatr Res 1996;39:410–4; Kilic M et al. Clin Biochem 2004;37:382–7; Street ME et al. Clin Endocrinol (Oxf) 2008;68:22–8; Federico G et al. Horm Res 1997;48:108–14; De Benedetti F et al. J Clin Invest 1997;99:643–50; De Benedetti F et al. Endocrinology 2001;142:4818–26; Bucuvalas JC et al. Pediatr Transplant 1997;1:73–9; Virmani A. Indian J Endocrinol Metab 2015;19 Suppl 1:S64–7</t>
+          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12:130–9; Arlien-Søborg MC et al. Pituitary 2025;28:57 (GRS)</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41">
@@ -16790,21 +18885,21 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>При ожирении, гиперкортицизме и болезнях почек ИФР-1 не отражает секрецию СТГ</t>
+          <t>ИФР-1 бывает низким и без дефицита СТГ: ось ломается в гипофизе, печени или крови</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>сравнения с контролем, n = 14–65; когорта, n = 40; семейная серия; описание случая</t>
+          <t>обзоры; клинические исследования; часть механизмов — опыты на мышах</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Argente J et al. J Clin Endocrinol Metab 1997;82:2076–83; Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12:130–9; Magiakou MA et al. J Clin Endocrinol Metab 1994;78:131–7; Blum WF et al. Pediatr Nephrol 1991;5:539–44; Tönshoff B, Fine RN. Adv Ren Replace Ther 1996;3:37–47; Guevara-Aguirre J et al. Rev Endocr Metab Disord 2021;22:59–70; Al-Ashwal AA et al. Horm Res Paediatr 2017;88:119–26; Moia S et al. Ital J Pediatr 2017;43:94; Gadelha MR et al. J Clin Endocrinol Metab 1999;84:249–56</t>
+          <t>Fazeli PK, Klibanski A. J Endocrinol 2014;220:R57–65; Wong SC et al. Endocr Rev 2016;37:62–110; Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12:130–9; Chernausek SD, Turner R. J Pediatr 1989;114:968–72; De Benedetti F et al. J Clin Invest 1997;99:643–50; Blum WF et al. Pediatr Nephrol 1991;5:539–44; Guevara-Aguirre J et al. Rev Endocr Metab Disord 2021;22:59–70</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42">
@@ -16813,21 +18908,21 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Низкий ИФР-1 сначала объясняют питанием, щитовидной железой и пубертатом, потом думают о СТГ</t>
+          <t>Низкий для возраста ИФР-1 дают гипотиреоз, задержка пубертата, голод и воспаление</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>порядок шагов: мнение докладчика; обзор: мнение экспертов; руководство Европейского общества детской гастроэнтерологии, гепатологии и питания</t>
+          <t>когорта, n = 15; сравнения с контролем, n = 14–36; опыты на мышах; обзоры</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12:130–9; Husby S et al. J Pediatr Gastroenterol Nutr 2020;70:141–56 (ESPGHAN)</t>
+          <t>Zamboni G et al. Acta Paediatr 2000;89:1050–5; Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12:130–9; Bereket A et al. Horm Res 2006;65:96–105; Zamboni G et al. Pediatr Res 1996;39:410–4; Kilic M et al. Clin Biochem 2004;37:382–7; Street ME et al. Clin Endocrinol (Oxf) 2008;68:22–8; Federico G et al. Horm Res 1997;48:108–14; De Benedetti F et al. J Clin Invest 1997;99:643–50; De Benedetti F et al. Endocrinology 2001;142:4818–26; Bucuvalas JC et al. Pediatr Transplant 1997;1:73–9; Virmani A. Indian J Endocrinol Metab 2015;19 Suppl 1:S64–7</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43">
@@ -16836,13 +18931,21 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>До проб на СТГ проверьте щитовидную железу, глюкокортикоиды, пубертат и кариотип</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr"/>
-      <c r="D43" s="2" t="inlineStr"/>
+          <t>При ожирении, гиперкортицизме и болезнях почек ИФР-1 не отражает секрецию СТГ</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>сравнения с контролем, n = 14–65; когорта, n = 40; семейная серия; описание случая</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Argente J et al. J Clin Endocrinol Metab 1997;82:2076–83; Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12:130–9; Magiakou MA et al. J Clin Endocrinol Metab 1994;78:131–7; Blum WF et al. Pediatr Nephrol 1991;5:539–44; Tönshoff B, Fine RN. Adv Ren Replace Ther 1996;3:37–47; Guevara-Aguirre J et al. Rev Endocr Metab Disord 2021;22:59–70; Al-Ashwal AA et al. Horm Res Paediatr 2017;88:119–26; Moia S et al. Ital J Pediatr 2017;43:94; Gadelha MR et al. J Clin Endocrinol Metab 1999;84:249–56</t>
+        </is>
+      </c>
       <c r="E43" s="2" t="n">
-        <v>88</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44">
@@ -16851,13 +18954,13 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Литература и лицензии изображений</t>
+          <t>Спасибо за внимание!</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Endo_short_stature/Таблица источников.xlsx
+++ b/Endo_short_stature/Таблица источников.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C110"/>
+  <dimension ref="A1:C111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1857,12 +1857,12 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Wang L et al. BMC Endocr Disord 2026;26(1), PMID 41933328</t>
+          <t>WHO Multicentre Growth Reference Study Group. Acta Paediatr Suppl 2006;450:76–85 (нормы ВОЗ); de Onis M et al. Bull World Health Organ 2007;85:660–7 (нормы ВОЗ)</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>6, 15, 24, 30</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Wasniewska M et al. Eur J Endocrinol 2009;160:417–21</t>
+          <t>Wang L et al. BMC Endocr Disord 2026;26(1), PMID 41933328</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -1887,12 +1887,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Wasserman JD et al. J Clin Oncol 2015;33:602–9</t>
+          <t>Wasniewska M et al. Eur J Endocrinol 2009;160:417–21</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Wehkalampi K et al. Horm Res 2007;68:99–104</t>
+          <t>Wasserman JD et al. J Clin Oncol 2015;33:602–9</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Wehkalampi K et al. J Clin Endocrinol Metab 2008;93:723–8</t>
+          <t>Wehkalampi K et al. Horm Res 2007;68:99–104</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Weise M et al. Proc Natl Acad Sci USA 2001;98:6871–6</t>
+          <t>Wehkalampi K et al. J Clin Endocrinol Metab 2008;93:723–8</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>5, 29</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Williams GR, Bassett JHD. J Endocrinol Invest 2018;41:99–109</t>
+          <t>Weise M et al. Proc Natl Acad Sci USA 2001;98:6871–6</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5, 29</t>
         </is>
       </c>
     </row>
@@ -1962,12 +1962,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12:130–9</t>
+          <t>Williams GR, Bassett JHD. J Endocrinol Invest 2018;41:99–109</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>35, 36, 39, 40, 41, 42</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Wong SC et al. Endocr Rev 2016;37:62–110</t>
+          <t>Wit JM et al. J Clin Res Pediatr Endocrinol 2020;12:130–9</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>35, 36, 39, 40, 41, 42</t>
         </is>
       </c>
     </row>
@@ -1992,12 +1992,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Wyatt DT et al. J Clin Endocrinol Metab 1998;83:3493–7</t>
+          <t>Wong SC et al. Endocr Rev 2016;37:62–110</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -2007,12 +2007,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Yamamoto M et al. Endocr J 2026, PMID 42386546</t>
+          <t>Wyatt DT et al. J Clin Endocrinol Metab 1998;83:3493–7</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Zamboni G et al. Acta Paediatr 2000;89:1050–5</t>
+          <t>Yamamoto M et al. Endocr J 2026, PMID 42386546</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Zamboni G et al. Pediatr Res 1996;39:410–4</t>
+          <t>Zamboni G et al. Acta Paediatr 2000;89:1050–5</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Zengin NŞ et al. J Clin Res Pediatr Endocrinol 2026;18:498–507</t>
+          <t>Zamboni G et al. Pediatr Res 1996;39:410–4</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -2067,12 +2067,12 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Zhang L et al. Cochrane Database Syst Rev 2014;(7):CD009471</t>
+          <t>Zengin NŞ et al. J Clin Res Pediatr Endocrinol 2026;18:498–507</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -2082,10 +2082,25 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
+          <t>Zhang L et al. Cochrane Database Syst Rev 2014;(7):CD009471</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>van Trotsenburg P et al. Thyroid 2021;31:387–419 (Endo-ERN, одобрено ESPE и ESE)</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -18002,7 +18017,7 @@
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3">
@@ -18113,11 +18128,11 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Salerno M et al. Front Endocrinol (Lausanne) 2026;16:1744280; Rohner F et al. Thyroid 2020;30:898–907</t>
+          <t>Salerno M et al. Front Endocrinol (Lausanne) 2026;16:1744280; Rohner F et al. Thyroid 2020;30:898–907; WHO Multicentre Growth Reference Study Group. Acta Paediatr Suppl 2006;450:76–85 (нормы ВОЗ); de Onis M et al. Bull World Health Organ 2007;85:660–7 (нормы ВОЗ)</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8">
@@ -18320,11 +18335,11 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Greening JE et al. J Endocrinol Invest 2006;29:885–7; Magiakou MA et al. N Engl J Med 1994;331:629–36; Yamamoto M et al. Endocr J 2026, PMID 42386546; Fleseriu M et al. Lancet Diabetes Endocrinol 2021;9:847–75 (Pituitary Society)</t>
+          <t>Greening JE et al. J Endocrinol Invest 2006;29:885–7; Magiakou MA et al. N Engl J Med 1994;331:629–36; Yamamoto M et al. Endocr J 2026, PMID 42386546; Fleseriu M et al. Lancet Diabetes Endocrinol 2021;9:847–75 (Pituitary Society); WHO Multicentre Growth Reference Study Group. Acta Paediatr Suppl 2006;450:76–85 (нормы ВОЗ); de Onis M et al. Bull World Health Organ 2007;85:660–7 (нормы ВОЗ)</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17">
@@ -18527,11 +18542,11 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Wehkalampi K et al. Horm Res 2007;68:99–104; Wehkalampi K et al. J Clin Endocrinol Metab 2008;93:723–8; Akın Kağızmanlı G et al. J Clin Res Pediatr Endocrinol 2025;17:410–8; Adan L et al. J Clin Endocrinol Metab 1994;78:478–82; Persani L et al. Endocrine 2021;71:681–8</t>
+          <t>Wehkalampi K et al. Horm Res 2007;68:99–104; Wehkalampi K et al. J Clin Endocrinol Metab 2008;93:723–8; Akın Kağızmanlı G et al. J Clin Res Pediatr Endocrinol 2025;17:410–8; Adan L et al. J Clin Endocrinol Metab 1994;78:478–82; Persani L et al. Endocrine 2021;71:681–8; WHO Multicentre Growth Reference Study Group. Acta Paediatr Suppl 2006;450:76–85 (нормы ВОЗ); de Onis M et al. Bull World Health Organ 2007;85:660–7 (нормы ВОЗ)</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
@@ -18665,7 +18680,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Gravholt CH et al. Eur J Endocrinol 2024;190:G53–G151; Gravholt CH et al. Lancet Diabetes Endocrinol 2026, PMID 42790437</t>
+          <t>Gravholt CH et al. Eur J Endocrinol 2024;190:G53–G151; Gravholt CH et al. Lancet Diabetes Endocrinol 2026, PMID 42790437; WHO Multicentre Growth Reference Study Group. Acta Paediatr Suppl 2006;450:76–85 (нормы ВОЗ); de Onis M et al. Bull World Health Organ 2007;85:660–7 (нормы ВОЗ)</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
